--- a/UAA/src/src/test/resources/com/ugapp/data/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/data/testdata.xlsx
@@ -1,31 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\divya\git\undergrad\UAA\src\src\test\resources\com\ugapp\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="9"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="test_suite" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="validData" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="ReviewPageData" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="PreviewPageData" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="LoginTest" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="PreAppDashboardTest" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="CreateAccountTest" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="FormerNameTest" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="ParentNameTest" sheetId="9" r:id="rId12"/>
-    <sheet state="visible" name="HomeAddressTest" sheetId="10" r:id="rId13"/>
-    <sheet state="visible" name="International HomeAddressTest" sheetId="11" r:id="rId14"/>
-    <sheet state="visible" name="GraduatingSchoolTest" sheetId="12" r:id="rId15"/>
-    <sheet state="visible" name="AddMaxHighSchoolTest" sheetId="13" r:id="rId16"/>
-    <sheet state="visible" name="overAllAcademicsTest" sheetId="14" r:id="rId17"/>
-    <sheet state="visible" name="CollegeUniversitiesTest" sheetId="15" r:id="rId18"/>
+    <sheet name="test_suite" sheetId="1" r:id="rId1"/>
+    <sheet name="validData" sheetId="2" r:id="rId2"/>
+    <sheet name="ReviewPageData" sheetId="3" r:id="rId3"/>
+    <sheet name="PreviewPageData" sheetId="4" r:id="rId4"/>
+    <sheet name="LoginTest" sheetId="5" r:id="rId5"/>
+    <sheet name="PreAppDashboardTest" sheetId="6" r:id="rId6"/>
+    <sheet name="CreateAccountTest" sheetId="7" r:id="rId7"/>
+    <sheet name="FormerNameTest" sheetId="8" r:id="rId8"/>
+    <sheet name="ParentNameTest" sheetId="9" r:id="rId9"/>
+    <sheet name="HomeAddressTest" sheetId="10" r:id="rId10"/>
+    <sheet name="International HomeAddressTest" sheetId="11" r:id="rId11"/>
+    <sheet name="GraduatingSchoolTest" sheetId="12" r:id="rId12"/>
+    <sheet name="AddMaxHighSchoolTest" sheetId="13" r:id="rId13"/>
+    <sheet name="overAllAcademicsTest" sheetId="14" r:id="rId14"/>
+    <sheet name="CollegeUniversitiesTest" sheetId="15" r:id="rId15"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>TCID</t>
   </si>
@@ -63,6 +69,26 @@
     <t>overAllAcademicsTest</t>
   </si>
   <si>
+    <t>Legal sex</t>
+  </si>
+  <si>
+    <t>X or another legal sex</t>
+  </si>
+  <si>
+    <t>Primary language spoken at home</t>
+  </si>
+  <si>
+    <t>Bavarian</t>
+  </si>
+  <si>
+    <t>Home address</t>
+  </si>
+  <si>
+    <t>Test Address line1 Test Address line2
+TestTestTestTestTestTestTestTest,Test State,Mayotte
+12345-678910</t>
+  </si>
+  <si>
     <t>email</t>
   </si>
   <si>
@@ -213,37 +239,40 @@
     <t>Mobile_Number</t>
   </si>
   <si>
+    <t>TestTestTestTestTestTestTestTestTestTestTestTestTest</t>
+  </si>
+  <si>
+    <t>1111111111111111</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Test Address line1</t>
+  </si>
+  <si>
+    <t>Test Address line2</t>
+  </si>
+  <si>
+    <t>Test City</t>
+  </si>
+  <si>
+    <t>12345-678910</t>
+  </si>
+  <si>
+    <t>Test State</t>
+  </si>
+  <si>
+    <t>6363052399</t>
+  </si>
+  <si>
+    <t>8150052399</t>
+  </si>
+  <si>
     <t>TestTestTestTestTestTestTestTestTestTestTest</t>
-  </si>
-  <si>
-    <t>1111111111111111</t>
-  </si>
-  <si>
-    <t>@</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>Test Address line1</t>
-  </si>
-  <si>
-    <t>Test Address line2</t>
-  </si>
-  <si>
-    <t>Test City</t>
-  </si>
-  <si>
-    <t>12345-678910</t>
-  </si>
-  <si>
-    <t>Test State</t>
-  </si>
-  <si>
-    <t>6363052399</t>
-  </si>
-  <si>
-    <t>8150052399</t>
   </si>
   <si>
     <t>SAISno</t>
@@ -336,57 +365,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="9">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
     </font>
@@ -396,7 +422,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -405,111 +431,46 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0"/>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -591,6 +552,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -617,24 +579,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -695,6 +658,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -703,17 +667,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.57"/>
-    <col customWidth="1" min="2" max="6" width="8.71"/>
+    <col min="1" max="1" width="24.57" customWidth="1"/>
+    <col min="2" max="6" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,7 +682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -729,7 +690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -737,7 +698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -745,7 +706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -753,7 +714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -761,7 +722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -769,7 +730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -777,7 +738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -785,7 +746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -793,43 +754,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
     </row>
@@ -2414,242 +2375,233 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="38.29"/>
-    <col customWidth="1" min="3" max="3" width="34.0"/>
-    <col customWidth="1" min="4" max="4" width="22.29"/>
-    <col customWidth="1" min="5" max="5" width="30.0"/>
-    <col customWidth="1" min="6" max="6" width="18.57"/>
-    <col customWidth="1" min="7" max="7" width="30.14"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18.57" customWidth="1"/>
+    <col min="7" max="7" width="30.14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="38.29"/>
-    <col customWidth="1" min="3" max="3" width="34.0"/>
-    <col customWidth="1" min="4" max="4" width="22.29"/>
-    <col customWidth="1" min="5" max="5" width="30.0"/>
-    <col customWidth="1" min="6" max="6" width="14.43"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.14"/>
-    <col customWidth="1" min="2" max="2" width="29.57"/>
-    <col customWidth="1" min="3" max="3" width="41.43"/>
-    <col customWidth="1" min="4" max="4" width="34.43"/>
-    <col customWidth="1" min="5" max="5" width="14.43"/>
+    <col min="1" max="1" width="27.14" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="41.43" customWidth="1"/>
+    <col min="4" max="4" width="34.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -2657,575 +2609,573 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="5" width="14.43"/>
+    <col min="1" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="14.43"/>
+    <col min="1" max="4" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="11"/>
       <c r="B6" s="12" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="31.0"/>
-    <col customWidth="1" min="2" max="2" width="27.43"/>
-    <col customWidth="1" min="3" max="3" width="51.0"/>
-    <col customWidth="1" min="4" max="4" width="22.43"/>
-    <col customWidth="1" min="5" max="5" width="14.43"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="27.43" customWidth="1"/>
+    <col min="3" max="3" width="51" customWidth="1"/>
+    <col min="4" max="4" width="22.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="36.86"/>
-    <col customWidth="1" min="2" max="2" width="41.14"/>
-    <col customWidth="1" min="3" max="3" width="20.43"/>
-    <col customWidth="1" min="4" max="4" width="20.14"/>
-    <col customWidth="1" min="5" max="5" width="31.43"/>
-    <col customWidth="1" min="6" max="6" width="24.43"/>
-    <col customWidth="1" min="7" max="7" width="26.71"/>
-    <col customWidth="1" min="12" max="12" width="40.71"/>
+    <col min="1" max="1" width="36.86" customWidth="1"/>
+    <col min="2" max="2" width="41.14" customWidth="1"/>
+    <col min="3" max="3" width="20.43" customWidth="1"/>
+    <col min="4" max="4" width="20.14" customWidth="1"/>
+    <col min="5" max="5" width="31.43" customWidth="1"/>
+    <col min="6" max="6" width="24.43" customWidth="1"/>
+    <col min="7" max="7" width="26.71" customWidth="1"/>
+    <col min="12" max="12" width="40.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="B1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
+      <c r="E1" s="1"/>
       <c r="F1" s="3"/>
       <c r="H1" s="3"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="4"/>
+      <c r="K1" s="1"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4"/>
+      <c r="A2" s="1"/>
       <c r="B2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="3"/>
       <c r="H2" s="3"/>
       <c r="J2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4"/>
+      <c r="A3" s="1"/>
       <c r="B3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4"/>
+      <c r="A4" s="1"/>
       <c r="B4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="3"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4"/>
+      <c r="A5" s="1"/>
       <c r="B5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
+      <c r="E5" s="1"/>
       <c r="F5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
+      <c r="K5" s="1"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="4"/>
+      <c r="A6" s="1"/>
       <c r="B6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="1"/>
       <c r="F6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="1"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
+      <c r="K6" s="1"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="1"/>
       <c r="B7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3"/>
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="1"/>
       <c r="F8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="3"/>
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="3"/>
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="3"/>
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="137.25" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="3"/>
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="3"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="4"/>
+      <c r="A11" s="1"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
+      <c r="E11" s="1"/>
       <c r="F11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
+      <c r="I11" s="1"/>
       <c r="J11" s="3"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="1"/>
       <c r="B12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
+      <c r="I12" s="1"/>
       <c r="J12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" ht="33.0" customHeight="1">
-      <c r="A13" s="4"/>
+    <row r="13" ht="33" customHeight="1">
+      <c r="A13" s="1"/>
       <c r="B13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="3"/>
       <c r="H13" s="3"/>
       <c r="J13" s="3"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="1"/>
       <c r="B14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="3"/>
       <c r="H14" s="3"/>
       <c r="J14" s="3"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="1"/>
       <c r="B15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="1"/>
       <c r="F15" s="3"/>
       <c r="H15" s="3"/>
       <c r="J15" s="3"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="4"/>
+      <c r="A16" s="1"/>
       <c r="B16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="1"/>
       <c r="F16" s="3"/>
       <c r="H16" s="3"/>
       <c r="J16" s="3"/>
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="4"/>
+      <c r="A17" s="1"/>
       <c r="B17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="1"/>
       <c r="F17" s="3"/>
       <c r="H17" s="3"/>
       <c r="J17" s="3"/>
@@ -3236,23 +3186,23 @@
       <c r="D18" s="3"/>
       <c r="H18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
+      <c r="K18" s="1"/>
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="4"/>
+      <c r="A19" s="1"/>
       <c r="B19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="K19" s="4"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="4"/>
+      <c r="A20" s="1"/>
       <c r="B20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="4"/>
+      <c r="A21" s="1"/>
       <c r="B21" s="3"/>
       <c r="H21" s="3"/>
     </row>
@@ -3261,17 +3211,17 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="4"/>
+      <c r="A23" s="1"/>
       <c r="B23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="4"/>
+      <c r="A24" s="1"/>
       <c r="B24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="4"/>
+      <c r="A25" s="1"/>
       <c r="B25" s="3"/>
       <c r="H25" s="3"/>
     </row>
@@ -3279,50 +3229,50 @@
       <c r="B26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="4"/>
+      <c r="A27" s="1"/>
       <c r="B27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="4"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="3"/>
       <c r="H27" s="3"/>
       <c r="J27" s="3"/>
       <c r="L27" s="3"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="4"/>
+      <c r="A28" s="1"/>
       <c r="B28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="3"/>
       <c r="H28" s="3"/>
       <c r="J28" s="3"/>
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="4"/>
+      <c r="A29" s="1"/>
       <c r="B29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="1"/>
       <c r="F29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="4"/>
+      <c r="I29" s="1"/>
       <c r="J29" s="3"/>
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="4"/>
+      <c r="A30" s="1"/>
       <c r="B30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="4"/>
+      <c r="A31" s="1"/>
       <c r="B31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="3"/>
       <c r="H31" s="3"/>
       <c r="L31" s="3"/>
@@ -3330,883 +3280,883 @@
     <row r="32" ht="14.25" customHeight="1">
       <c r="B32" s="3"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="1"/>
       <c r="F32" s="3"/>
       <c r="H32" s="3"/>
       <c r="L32" s="3"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="4"/>
+      <c r="A33" s="1"/>
       <c r="B33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="1"/>
       <c r="F33" s="3"/>
       <c r="H33" s="3"/>
       <c r="J33" s="3"/>
       <c r="L33" s="3"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="4"/>
+      <c r="A34" s="1"/>
       <c r="B34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="4"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="4"/>
+      <c r="I34" s="1"/>
       <c r="J34" s="3"/>
       <c r="L34" s="3"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="4"/>
+      <c r="A35" s="1"/>
       <c r="B35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="4"/>
+      <c r="I35" s="1"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="4"/>
+      <c r="K35" s="1"/>
       <c r="L35" s="3"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="1"/>
       <c r="B36" s="3"/>
       <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="3"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="1"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="4"/>
+      <c r="K36" s="1"/>
       <c r="L36" s="3"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="4"/>
+      <c r="A37" s="1"/>
       <c r="B37" s="3"/>
       <c r="D37" s="3"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="4"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="4"/>
+      <c r="K37" s="1"/>
       <c r="L37" s="3"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="1"/>
       <c r="B38" s="3"/>
       <c r="D38" s="3"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="4"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="3"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="1"/>
       <c r="B39" s="3"/>
       <c r="D39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="4"/>
+      <c r="I39" s="1"/>
       <c r="J39" s="3"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="4"/>
+      <c r="A40" s="1"/>
       <c r="B40" s="3"/>
       <c r="D40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="4"/>
+      <c r="I40" s="1"/>
       <c r="J40" s="3"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="4"/>
+      <c r="A41" s="1"/>
       <c r="B41" s="3"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="4"/>
+      <c r="E41" s="1"/>
       <c r="F41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="4"/>
+      <c r="I41" s="1"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="4"/>
+      <c r="K41" s="1"/>
       <c r="L41" s="3"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="4"/>
+      <c r="A42" s="1"/>
       <c r="B42" s="3"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="1"/>
       <c r="F42" s="3"/>
       <c r="H42" s="3"/>
-      <c r="I42" s="4"/>
+      <c r="I42" s="1"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="4"/>
+      <c r="K42" s="1"/>
       <c r="L42" s="3"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="4"/>
+      <c r="A43" s="1"/>
       <c r="B43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="4"/>
+      <c r="E43" s="1"/>
       <c r="F43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="4"/>
+      <c r="I43" s="1"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="4"/>
+      <c r="K43" s="1"/>
       <c r="L43" s="3"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="4"/>
+      <c r="A44" s="1"/>
       <c r="B44" s="3"/>
       <c r="D44" s="3"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="4"/>
+      <c r="I44" s="1"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="4"/>
+      <c r="K44" s="1"/>
       <c r="L44" s="3"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="4"/>
+      <c r="A45" s="1"/>
       <c r="B45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="1"/>
       <c r="F45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="4"/>
+      <c r="I45" s="1"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="4"/>
+      <c r="K45" s="1"/>
       <c r="L45" s="3"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="4"/>
+      <c r="A46" s="1"/>
       <c r="B46" s="3"/>
       <c r="D46" s="3"/>
-      <c r="E46" s="4"/>
+      <c r="E46" s="1"/>
       <c r="F46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="4"/>
+      <c r="I46" s="1"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="4"/>
+      <c r="K46" s="1"/>
       <c r="L46" s="3"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="4"/>
+      <c r="A47" s="1"/>
       <c r="B47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="4"/>
+      <c r="E47" s="1"/>
       <c r="F47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="4"/>
+      <c r="I47" s="1"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="4"/>
+      <c r="K47" s="1"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="4"/>
+      <c r="A48" s="1"/>
       <c r="B48" s="3"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="4"/>
+      <c r="E48" s="1"/>
       <c r="F48" s="3"/>
       <c r="H48" s="3"/>
-      <c r="I48" s="4"/>
+      <c r="I48" s="1"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="4"/>
+      <c r="K48" s="1"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="4"/>
+      <c r="A49" s="1"/>
       <c r="B49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="1"/>
       <c r="F49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="4"/>
+      <c r="I49" s="1"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="4"/>
+      <c r="K49" s="1"/>
       <c r="L49" s="3"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="4"/>
+      <c r="A50" s="1"/>
       <c r="B50" s="3"/>
       <c r="D50" s="3"/>
       <c r="H50" s="3"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="4"/>
+      <c r="A51" s="1"/>
       <c r="B51" s="3"/>
       <c r="H51" s="3"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="4"/>
+      <c r="A52" s="1"/>
       <c r="B52" s="3"/>
       <c r="H52" s="3"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="4"/>
+      <c r="A53" s="1"/>
       <c r="B53" s="3"/>
       <c r="H53" s="3"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="4"/>
+      <c r="A54" s="1"/>
       <c r="B54" s="3"/>
       <c r="H54" s="3"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="4"/>
+      <c r="A55" s="1"/>
       <c r="B55" s="3"/>
       <c r="H55" s="3"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="4"/>
+      <c r="A56" s="1"/>
       <c r="B56" s="3"/>
       <c r="H56" s="3"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="4"/>
+      <c r="A57" s="1"/>
       <c r="B57" s="3"/>
       <c r="H57" s="3"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="4"/>
+      <c r="A58" s="1"/>
       <c r="B58" s="3"/>
       <c r="H58" s="3"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="4"/>
+      <c r="A59" s="1"/>
       <c r="B59" s="3"/>
       <c r="H59" s="3"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="4"/>
+      <c r="A60" s="1"/>
       <c r="B60" s="3"/>
       <c r="H60" s="3"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="4"/>
+      <c r="A61" s="1"/>
       <c r="B61" s="3"/>
       <c r="H61" s="3"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="4"/>
+      <c r="A62" s="1"/>
       <c r="B62" s="3"/>
       <c r="H62" s="3"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="4"/>
+      <c r="A63" s="1"/>
       <c r="B63" s="3"/>
       <c r="H63" s="3"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="4"/>
+      <c r="A64" s="1"/>
       <c r="B64" s="3"/>
       <c r="H64" s="3"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="4"/>
+      <c r="A65" s="1"/>
       <c r="B65" s="3"/>
       <c r="H65" s="3"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="4"/>
+      <c r="A66" s="1"/>
       <c r="B66" s="3"/>
       <c r="H66" s="3"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="4"/>
+      <c r="A67" s="1"/>
       <c r="B67" s="3"/>
       <c r="H67" s="3"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="4"/>
+      <c r="A68" s="1"/>
       <c r="B68" s="3"/>
       <c r="H68" s="3"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="4"/>
+      <c r="A69" s="1"/>
       <c r="B69" s="3"/>
       <c r="H69" s="3"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="4"/>
+      <c r="A70" s="1"/>
       <c r="B70" s="3"/>
       <c r="H70" s="3"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="4"/>
+      <c r="A71" s="1"/>
       <c r="B71" s="3"/>
       <c r="H71" s="3"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="4"/>
+      <c r="A72" s="1"/>
       <c r="B72" s="3"/>
       <c r="H72" s="3"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="4"/>
+      <c r="A73" s="1"/>
       <c r="B73" s="3"/>
       <c r="H73" s="3"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="4"/>
+      <c r="A74" s="1"/>
       <c r="B74" s="3"/>
       <c r="H74" s="3"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="4"/>
+      <c r="A75" s="1"/>
       <c r="B75" s="3"/>
       <c r="H75" s="3"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="4"/>
+      <c r="A76" s="1"/>
       <c r="B76" s="3"/>
       <c r="H76" s="3"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="4"/>
+      <c r="A77" s="1"/>
       <c r="B77" s="3"/>
       <c r="H77" s="3"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="4"/>
+      <c r="A78" s="1"/>
       <c r="B78" s="3"/>
       <c r="H78" s="3"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="4"/>
+      <c r="A79" s="1"/>
       <c r="B79" s="3"/>
       <c r="H79" s="3"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="4"/>
+      <c r="A80" s="1"/>
       <c r="B80" s="3"/>
       <c r="H80" s="3"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="4"/>
+      <c r="A81" s="1"/>
       <c r="B81" s="3"/>
       <c r="H81" s="3"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="4"/>
+      <c r="A82" s="1"/>
       <c r="B82" s="3"/>
       <c r="H82" s="3"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="4"/>
+      <c r="A83" s="1"/>
       <c r="B83" s="3"/>
       <c r="H83" s="3"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="4"/>
+      <c r="A84" s="1"/>
       <c r="B84" s="3"/>
       <c r="H84" s="3"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="4"/>
+      <c r="A85" s="1"/>
       <c r="B85" s="3"/>
       <c r="H85" s="3"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="4"/>
+      <c r="A86" s="1"/>
       <c r="B86" s="3"/>
       <c r="H86" s="3"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="4"/>
+      <c r="A87" s="1"/>
       <c r="B87" s="3"/>
       <c r="H87" s="3"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="4"/>
+      <c r="A88" s="1"/>
       <c r="B88" s="3"/>
       <c r="H88" s="3"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="4"/>
+      <c r="A89" s="1"/>
       <c r="B89" s="3"/>
       <c r="H89" s="3"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="4"/>
+      <c r="A90" s="1"/>
       <c r="B90" s="3"/>
       <c r="H90" s="3"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="4"/>
+      <c r="A91" s="1"/>
       <c r="B91" s="3"/>
       <c r="H91" s="3"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="4"/>
+      <c r="A92" s="1"/>
       <c r="B92" s="3"/>
       <c r="H92" s="3"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="4"/>
+      <c r="A93" s="1"/>
       <c r="B93" s="3"/>
       <c r="H93" s="3"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="4"/>
+      <c r="A94" s="1"/>
       <c r="B94" s="3"/>
       <c r="H94" s="3"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="4"/>
+      <c r="A95" s="1"/>
       <c r="B95" s="3"/>
       <c r="H95" s="3"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="4"/>
+      <c r="A96" s="1"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
-      <c r="E96" s="4"/>
+      <c r="E96" s="1"/>
       <c r="F96" s="3"/>
       <c r="H96" s="3"/>
-      <c r="I96" s="4"/>
+      <c r="I96" s="1"/>
       <c r="J96" s="3"/>
-      <c r="K96" s="4"/>
+      <c r="K96" s="1"/>
       <c r="L96" s="3"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="4"/>
+      <c r="A97" s="1"/>
       <c r="B97" s="3"/>
-      <c r="E97" s="4"/>
+      <c r="E97" s="1"/>
       <c r="F97" s="3"/>
       <c r="H97" s="3"/>
-      <c r="I97" s="4"/>
+      <c r="I97" s="1"/>
       <c r="J97" s="3"/>
-      <c r="K97" s="4"/>
+      <c r="K97" s="1"/>
       <c r="L97" s="3"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="4"/>
+      <c r="A98" s="1"/>
       <c r="B98" s="3"/>
-      <c r="E98" s="4"/>
+      <c r="E98" s="1"/>
       <c r="F98" s="3"/>
       <c r="H98" s="3"/>
-      <c r="I98" s="4"/>
+      <c r="I98" s="1"/>
       <c r="J98" s="3"/>
-      <c r="K98" s="4"/>
+      <c r="K98" s="1"/>
       <c r="L98" s="3"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="4"/>
+      <c r="A99" s="1"/>
       <c r="B99" s="3"/>
-      <c r="E99" s="4"/>
+      <c r="E99" s="1"/>
       <c r="F99" s="3"/>
       <c r="H99" s="3"/>
-      <c r="I99" s="4"/>
+      <c r="I99" s="1"/>
       <c r="J99" s="3"/>
-      <c r="K99" s="4"/>
+      <c r="K99" s="1"/>
       <c r="L99" s="3"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="4"/>
+      <c r="A100" s="1"/>
       <c r="B100" s="3"/>
-      <c r="E100" s="4"/>
+      <c r="E100" s="1"/>
       <c r="F100" s="3"/>
       <c r="H100" s="3"/>
-      <c r="I100" s="4"/>
+      <c r="I100" s="1"/>
       <c r="J100" s="3"/>
-      <c r="K100" s="4"/>
+      <c r="K100" s="1"/>
       <c r="L100" s="3"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="4"/>
+      <c r="A101" s="1"/>
       <c r="B101" s="3"/>
-      <c r="E101" s="4"/>
+      <c r="E101" s="1"/>
       <c r="F101" s="3"/>
       <c r="H101" s="3"/>
-      <c r="I101" s="4"/>
+      <c r="I101" s="1"/>
       <c r="J101" s="3"/>
-      <c r="K101" s="4"/>
+      <c r="K101" s="1"/>
       <c r="L101" s="3"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="4"/>
+      <c r="A102" s="1"/>
       <c r="B102" s="3"/>
-      <c r="E102" s="4"/>
+      <c r="E102" s="1"/>
       <c r="F102" s="3"/>
       <c r="H102" s="3"/>
-      <c r="I102" s="4"/>
+      <c r="I102" s="1"/>
       <c r="J102" s="3"/>
-      <c r="K102" s="4"/>
+      <c r="K102" s="1"/>
       <c r="L102" s="3"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="4"/>
+      <c r="A103" s="1"/>
       <c r="B103" s="3"/>
-      <c r="E103" s="4"/>
+      <c r="E103" s="1"/>
       <c r="F103" s="3"/>
       <c r="H103" s="3"/>
-      <c r="I103" s="4"/>
+      <c r="I103" s="1"/>
       <c r="J103" s="3"/>
-      <c r="K103" s="4"/>
+      <c r="K103" s="1"/>
       <c r="L103" s="3"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="4"/>
+      <c r="A104" s="1"/>
       <c r="B104" s="3"/>
-      <c r="E104" s="4"/>
+      <c r="E104" s="1"/>
       <c r="F104" s="3"/>
       <c r="H104" s="3"/>
-      <c r="I104" s="4"/>
+      <c r="I104" s="1"/>
       <c r="J104" s="3"/>
-      <c r="K104" s="4"/>
+      <c r="K104" s="1"/>
       <c r="L104" s="3"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="4"/>
+      <c r="A105" s="1"/>
       <c r="B105" s="3"/>
-      <c r="E105" s="4"/>
+      <c r="E105" s="1"/>
       <c r="F105" s="3"/>
       <c r="H105" s="3"/>
-      <c r="K105" s="4"/>
+      <c r="K105" s="1"/>
       <c r="L105" s="3"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="4"/>
+      <c r="A106" s="1"/>
       <c r="B106" s="3"/>
-      <c r="E106" s="4"/>
+      <c r="E106" s="1"/>
       <c r="F106" s="3"/>
       <c r="H106" s="3"/>
-      <c r="K106" s="4"/>
+      <c r="K106" s="1"/>
       <c r="L106" s="3"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="4"/>
+      <c r="A107" s="1"/>
       <c r="B107" s="3"/>
-      <c r="E107" s="4"/>
+      <c r="E107" s="1"/>
       <c r="F107" s="3"/>
       <c r="H107" s="3"/>
-      <c r="K107" s="4"/>
+      <c r="K107" s="1"/>
       <c r="L107" s="3"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="4"/>
+      <c r="A108" s="1"/>
       <c r="B108" s="3"/>
-      <c r="E108" s="4"/>
+      <c r="E108" s="1"/>
       <c r="F108" s="3"/>
       <c r="H108" s="3"/>
-      <c r="K108" s="4"/>
+      <c r="K108" s="1"/>
       <c r="L108" s="3"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="4"/>
+      <c r="A109" s="1"/>
       <c r="B109" s="3"/>
-      <c r="E109" s="4"/>
+      <c r="E109" s="1"/>
       <c r="F109" s="3"/>
       <c r="H109" s="3"/>
-      <c r="K109" s="4"/>
+      <c r="K109" s="1"/>
       <c r="L109" s="3"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="4"/>
+      <c r="A110" s="1"/>
       <c r="B110" s="3"/>
-      <c r="E110" s="4"/>
+      <c r="E110" s="1"/>
       <c r="F110" s="3"/>
       <c r="H110" s="3"/>
-      <c r="K110" s="4"/>
+      <c r="K110" s="1"/>
       <c r="L110" s="3"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="4"/>
+      <c r="A111" s="1"/>
       <c r="B111" s="3"/>
-      <c r="E111" s="4"/>
+      <c r="E111" s="1"/>
       <c r="F111" s="3"/>
       <c r="H111" s="3"/>
-      <c r="K111" s="4"/>
+      <c r="K111" s="1"/>
       <c r="L111" s="3"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="4"/>
+      <c r="A112" s="1"/>
       <c r="B112" s="3"/>
-      <c r="E112" s="4"/>
+      <c r="E112" s="1"/>
       <c r="F112" s="3"/>
       <c r="H112" s="3"/>
-      <c r="K112" s="4"/>
+      <c r="K112" s="1"/>
       <c r="L112" s="3"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="4"/>
+      <c r="A113" s="1"/>
       <c r="B113" s="3"/>
-      <c r="E113" s="4"/>
+      <c r="E113" s="1"/>
       <c r="F113" s="3"/>
       <c r="H113" s="3"/>
-      <c r="K113" s="4"/>
+      <c r="K113" s="1"/>
       <c r="L113" s="3"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="4"/>
+      <c r="A114" s="1"/>
       <c r="B114" s="3"/>
-      <c r="E114" s="4"/>
+      <c r="E114" s="1"/>
       <c r="F114" s="3"/>
       <c r="H114" s="3"/>
-      <c r="K114" s="4"/>
+      <c r="K114" s="1"/>
       <c r="L114" s="3"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="4"/>
+      <c r="A115" s="1"/>
       <c r="B115" s="3"/>
       <c r="D115" s="3"/>
-      <c r="E115" s="4"/>
+      <c r="E115" s="1"/>
       <c r="F115" s="3"/>
       <c r="H115" s="3"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="4"/>
+      <c r="A116" s="1"/>
       <c r="B116" s="3"/>
-      <c r="E116" s="4"/>
+      <c r="E116" s="1"/>
       <c r="F116" s="3"/>
       <c r="H116" s="3"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="4"/>
+      <c r="A117" s="1"/>
       <c r="B117" s="3"/>
-      <c r="E117" s="4"/>
+      <c r="E117" s="1"/>
       <c r="F117" s="3"/>
       <c r="H117" s="3"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="4"/>
+      <c r="A118" s="1"/>
       <c r="B118" s="3"/>
-      <c r="E118" s="4"/>
+      <c r="E118" s="1"/>
       <c r="F118" s="3"/>
       <c r="H118" s="3"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="4"/>
+      <c r="A119" s="1"/>
       <c r="B119" s="3"/>
-      <c r="E119" s="4"/>
+      <c r="E119" s="1"/>
       <c r="F119" s="3"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="4"/>
+      <c r="A120" s="1"/>
       <c r="B120" s="3"/>
-      <c r="E120" s="4"/>
+      <c r="E120" s="1"/>
       <c r="F120" s="3"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="4"/>
+      <c r="A121" s="1"/>
       <c r="B121" s="3"/>
-      <c r="E121" s="4"/>
+      <c r="E121" s="1"/>
       <c r="F121" s="3"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="4"/>
+      <c r="A122" s="1"/>
       <c r="B122" s="3"/>
-      <c r="E122" s="4"/>
+      <c r="E122" s="1"/>
       <c r="F122" s="3"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="4"/>
+      <c r="A123" s="1"/>
       <c r="B123" s="3"/>
-      <c r="E123" s="4"/>
+      <c r="E123" s="1"/>
       <c r="F123" s="3"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="4"/>
+      <c r="A124" s="1"/>
       <c r="B124" s="3"/>
-      <c r="E124" s="4"/>
+      <c r="E124" s="1"/>
       <c r="F124" s="3"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="4"/>
+      <c r="A125" s="1"/>
       <c r="B125" s="3"/>
-      <c r="E125" s="4"/>
+      <c r="E125" s="1"/>
       <c r="F125" s="3"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="4"/>
+      <c r="A126" s="1"/>
       <c r="B126" s="3"/>
       <c r="D126" s="3"/>
-      <c r="E126" s="4"/>
+      <c r="E126" s="1"/>
       <c r="F126" s="3"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="B127" s="3"/>
-      <c r="E127" s="4"/>
+      <c r="E127" s="1"/>
       <c r="F127" s="3"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="B128" s="3"/>
-      <c r="E128" s="4"/>
+      <c r="E128" s="1"/>
       <c r="F128" s="3"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="4"/>
+      <c r="A129" s="1"/>
       <c r="B129" s="3"/>
-      <c r="E129" s="4"/>
+      <c r="E129" s="1"/>
       <c r="F129" s="3"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="4"/>
+      <c r="A130" s="1"/>
       <c r="B130" s="3"/>
-      <c r="E130" s="4"/>
+      <c r="E130" s="1"/>
       <c r="F130" s="3"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="4"/>
+      <c r="A131" s="1"/>
       <c r="B131" s="3"/>
-      <c r="E131" s="4"/>
+      <c r="E131" s="1"/>
       <c r="F131" s="3"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="4"/>
+      <c r="A132" s="1"/>
       <c r="B132" s="3"/>
-      <c r="E132" s="4"/>
+      <c r="E132" s="1"/>
       <c r="F132" s="3"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="B133" s="3"/>
-      <c r="E133" s="4"/>
+      <c r="E133" s="1"/>
       <c r="F133" s="3"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="B134" s="3"/>
-      <c r="E134" s="4"/>
+      <c r="E134" s="1"/>
       <c r="F134" s="3"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="B135" s="3"/>
-      <c r="E135" s="4"/>
+      <c r="E135" s="1"/>
       <c r="F135" s="3"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="B136" s="3"/>
-      <c r="E136" s="4"/>
+      <c r="E136" s="1"/>
       <c r="F136" s="3"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="B137" s="3"/>
-      <c r="E137" s="4"/>
+      <c r="E137" s="1"/>
       <c r="F137" s="3"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="4"/>
+      <c r="A138" s="1"/>
       <c r="B138" s="3"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="4"/>
+      <c r="A139" s="1"/>
       <c r="B139" s="3"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="4"/>
+      <c r="A140" s="1"/>
       <c r="B140" s="3"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="4"/>
+      <c r="A141" s="1"/>
       <c r="B141" s="3"/>
-      <c r="E141" s="4"/>
+      <c r="E141" s="1"/>
       <c r="F141" s="3"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="4"/>
+      <c r="A142" s="1"/>
       <c r="B142" s="3"/>
-      <c r="E142" s="4"/>
+      <c r="E142" s="1"/>
       <c r="F142" s="3"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="4"/>
+      <c r="A143" s="1"/>
       <c r="B143" s="3"/>
-      <c r="E143" s="4"/>
+      <c r="E143" s="1"/>
       <c r="F143" s="3"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="4"/>
+      <c r="A144" s="1"/>
       <c r="B144" s="3"/>
-      <c r="E144" s="4"/>
+      <c r="E144" s="1"/>
       <c r="F144" s="3"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="4"/>
+      <c r="A145" s="1"/>
       <c r="B145" s="3"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="4"/>
+      <c r="A146" s="1"/>
       <c r="B146" s="3"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="4"/>
+      <c r="A147" s="1"/>
       <c r="B147" s="3"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="4"/>
+      <c r="A148" s="1"/>
       <c r="B148" s="3"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="4"/>
+      <c r="A149" s="1"/>
       <c r="B149" s="3"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
       <c r="B150" s="3"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="4"/>
+      <c r="A151" s="1"/>
       <c r="B151" s="3"/>
-      <c r="E151" s="4"/>
+      <c r="E151" s="1"/>
       <c r="F151" s="3"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="4"/>
+      <c r="A152" s="1"/>
       <c r="B152" s="3"/>
-      <c r="E152" s="4"/>
+      <c r="E152" s="1"/>
       <c r="F152" s="3"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="4"/>
+      <c r="A153" s="1"/>
       <c r="B153" s="3"/>
-      <c r="E153" s="4"/>
+      <c r="E153" s="1"/>
       <c r="F153" s="3"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="4"/>
+      <c r="A154" s="1"/>
       <c r="B154" s="3"/>
-      <c r="E154" s="4"/>
+      <c r="E154" s="1"/>
       <c r="F154" s="3"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="4"/>
+      <c r="A155" s="1"/>
       <c r="B155" s="3"/>
-      <c r="E155" s="4"/>
+      <c r="E155" s="1"/>
       <c r="F155" s="3"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="4"/>
+      <c r="A156" s="1"/>
       <c r="B156" s="3"/>
-      <c r="E156" s="4"/>
+      <c r="E156" s="1"/>
       <c r="F156" s="3"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="4"/>
+      <c r="A157" s="1"/>
       <c r="B157" s="3"/>
-      <c r="E157" s="4"/>
+      <c r="E157" s="1"/>
       <c r="F157" s="3"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="4"/>
+      <c r="A158" s="1"/>
       <c r="B158" s="3"/>
-      <c r="E158" s="4"/>
+      <c r="E158" s="1"/>
       <c r="F158" s="3"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="4"/>
+      <c r="A159" s="1"/>
       <c r="B159" s="3"/>
-      <c r="E159" s="4"/>
+      <c r="E159" s="1"/>
       <c r="F159" s="3"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="4"/>
+      <c r="A160" s="1"/>
       <c r="B160" s="3"/>
-      <c r="E160" s="4"/>
+      <c r="E160" s="1"/>
       <c r="F160" s="3"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="4"/>
+      <c r="A161" s="1"/>
       <c r="B161" s="3"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="4"/>
+      <c r="A162" s="1"/>
       <c r="B162" s="3"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -4217,12 +4167,12 @@
     </row>
     <row r="165" ht="14.25" customHeight="1">
       <c r="B165" s="3"/>
-      <c r="E165" s="4"/>
+      <c r="E165" s="1"/>
       <c r="F165" s="3"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="B166" s="3"/>
-      <c r="E166" s="4"/>
+      <c r="E166" s="1"/>
       <c r="F166" s="3"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -4244,39 +4194,39 @@
       <c r="B171" s="3"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="4"/>
+      <c r="A172" s="1"/>
       <c r="B172" s="3"/>
-      <c r="E172" s="4"/>
+      <c r="E172" s="1"/>
       <c r="F172" s="3"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="4"/>
+      <c r="A173" s="1"/>
       <c r="B173" s="3"/>
-      <c r="E173" s="4"/>
+      <c r="E173" s="1"/>
       <c r="F173" s="3"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="A174" s="4"/>
+      <c r="A174" s="1"/>
       <c r="B174" s="3"/>
-      <c r="E174" s="4"/>
+      <c r="E174" s="1"/>
       <c r="F174" s="3"/>
     </row>
     <row r="175" ht="14.25" customHeight="1">
-      <c r="A175" s="4"/>
+      <c r="A175" s="1"/>
       <c r="B175" s="3"/>
-      <c r="E175" s="4"/>
+      <c r="E175" s="1"/>
       <c r="F175" s="3"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
-      <c r="A176" s="4"/>
+      <c r="A176" s="1"/>
       <c r="B176" s="3"/>
-      <c r="E176" s="4"/>
+      <c r="E176" s="1"/>
       <c r="F176" s="3"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c r="A177" s="4"/>
+      <c r="A177" s="1"/>
       <c r="B177" s="3"/>
-      <c r="E177" s="4"/>
+      <c r="E177" s="1"/>
       <c r="F177" s="3"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -4309,75 +4259,75 @@
       <c r="B187" s="3"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c r="A188" s="4"/>
+      <c r="A188" s="1"/>
       <c r="B188" s="3"/>
-      <c r="E188" s="4"/>
+      <c r="E188" s="1"/>
       <c r="F188" s="3"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="4"/>
+      <c r="A189" s="1"/>
       <c r="B189" s="3"/>
-      <c r="E189" s="4"/>
+      <c r="E189" s="1"/>
       <c r="F189" s="3"/>
     </row>
     <row r="190" ht="14.25" customHeight="1">
-      <c r="A190" s="4"/>
+      <c r="A190" s="1"/>
       <c r="B190" s="3"/>
-      <c r="E190" s="4"/>
+      <c r="E190" s="1"/>
       <c r="F190" s="3"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c r="A191" s="4"/>
+      <c r="A191" s="1"/>
       <c r="B191" s="3"/>
-      <c r="E191" s="4"/>
+      <c r="E191" s="1"/>
       <c r="F191" s="3"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c r="A192" s="4"/>
+      <c r="A192" s="1"/>
       <c r="B192" s="3"/>
-      <c r="E192" s="4"/>
+      <c r="E192" s="1"/>
       <c r="F192" s="3"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
-      <c r="A193" s="4"/>
+      <c r="A193" s="1"/>
       <c r="B193" s="3"/>
-      <c r="E193" s="4"/>
+      <c r="E193" s="1"/>
       <c r="F193" s="3"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="4"/>
+      <c r="A194" s="1"/>
       <c r="B194" s="3"/>
-      <c r="E194" s="4"/>
+      <c r="E194" s="1"/>
       <c r="F194" s="3"/>
     </row>
     <row r="195" ht="14.25" customHeight="1">
-      <c r="A195" s="4"/>
+      <c r="A195" s="1"/>
       <c r="B195" s="3"/>
-      <c r="E195" s="4"/>
+      <c r="E195" s="1"/>
       <c r="F195" s="3"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
-      <c r="A196" s="4"/>
+      <c r="A196" s="1"/>
       <c r="B196" s="3"/>
-      <c r="E196" s="4"/>
+      <c r="E196" s="1"/>
       <c r="F196" s="3"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="4"/>
+      <c r="A197" s="1"/>
       <c r="B197" s="3"/>
-      <c r="E197" s="4"/>
+      <c r="E197" s="1"/>
       <c r="F197" s="3"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
-      <c r="A198" s="4"/>
+      <c r="A198" s="1"/>
       <c r="B198" s="3"/>
-      <c r="E198" s="4"/>
+      <c r="E198" s="1"/>
       <c r="F198" s="3"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="4"/>
+      <c r="A199" s="1"/>
       <c r="B199" s="3"/>
-      <c r="E199" s="4"/>
+      <c r="E199" s="1"/>
       <c r="F199" s="3"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
@@ -5186,1244 +5136,1239 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="13.14"/>
-    <col customWidth="1" min="2" max="2" width="23.71"/>
-    <col customWidth="1" min="3" max="3" width="45.14"/>
-    <col customWidth="1" min="4" max="4" width="14.57"/>
-    <col customWidth="1" min="5" max="5" width="60.0"/>
-    <col customWidth="1" min="6" max="6" width="25.14"/>
+    <col min="1" max="1" width="13.14" customWidth="1"/>
+    <col min="2" max="2" width="23.71" customWidth="1"/>
+    <col min="3" max="3" width="45.14" customWidth="1"/>
+    <col min="4" max="4" width="14.57" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="25.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="4"/>
+      <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
+      <c r="E1" s="1"/>
       <c r="F1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="4"/>
+      <c r="K1" s="1"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4"/>
+      <c r="A2" s="1"/>
       <c r="B2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
+      <c r="I2" s="1"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4"/>
+      <c r="A3" s="1"/>
       <c r="B3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
+      <c r="I3" s="1"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
+      <c r="K3" s="1"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4"/>
+      <c r="A4" s="1"/>
       <c r="B4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
+      <c r="I4" s="1"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
+      <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4"/>
+      <c r="A5" s="1"/>
       <c r="B5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
+      <c r="E5" s="1"/>
       <c r="F5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
+      <c r="K5" s="1"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="4"/>
+      <c r="A6" s="1"/>
       <c r="B6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="1"/>
       <c r="F6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="1"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
+      <c r="K6" s="1"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="1"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="1"/>
       <c r="F7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
+      <c r="I7" s="1"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="1"/>
       <c r="L7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="4"/>
+      <c r="A8" s="1"/>
       <c r="B8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="1"/>
       <c r="F8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="4"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
+      <c r="K8" s="1"/>
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="4"/>
+      <c r="A9" s="1"/>
       <c r="B9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="4"/>
+      <c r="I9" s="1"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
+      <c r="K9" s="1"/>
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="4"/>
+      <c r="A10" s="1"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
+      <c r="K10" s="1"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="4"/>
+      <c r="A11" s="1"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
+      <c r="E11" s="1"/>
       <c r="F11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
+      <c r="I11" s="1"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
+      <c r="K11" s="1"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="1"/>
       <c r="B12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
+      <c r="I12" s="1"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
+      <c r="K12" s="1"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" ht="33.0" customHeight="1">
-      <c r="A13" s="4"/>
+    <row r="13" ht="33" customHeight="1">
+      <c r="A13" s="1"/>
       <c r="B13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
+      <c r="I13" s="1"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
+      <c r="K13" s="1"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="1"/>
       <c r="B14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="4"/>
+      <c r="I14" s="1"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
+      <c r="K14" s="1"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="1"/>
       <c r="B15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="1"/>
       <c r="F15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="4"/>
+      <c r="I15" s="1"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
+      <c r="K15" s="1"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="4"/>
+      <c r="A16" s="1"/>
       <c r="B16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="1"/>
       <c r="F16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="1"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
+      <c r="K16" s="1"/>
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="4"/>
+      <c r="A17" s="1"/>
       <c r="B17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="1"/>
       <c r="F17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="4"/>
+      <c r="I17" s="1"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
+      <c r="K17" s="1"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="4"/>
+      <c r="A18" s="1"/>
       <c r="B18" s="3"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="1"/>
       <c r="F18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="4"/>
+      <c r="I18" s="1"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
+      <c r="K18" s="1"/>
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="4"/>
+      <c r="A19" s="1"/>
       <c r="B19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="4"/>
+      <c r="E19" s="1"/>
       <c r="F19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="4"/>
+      <c r="I19" s="1"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="4"/>
+      <c r="A20" s="1"/>
       <c r="B20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="4"/>
+      <c r="E20" s="1"/>
       <c r="F20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="4"/>
+      <c r="I20" s="1"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="4"/>
+      <c r="A21" s="1"/>
       <c r="B21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="4"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="4"/>
+      <c r="I21" s="1"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="3"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="4"/>
+      <c r="A22" s="1"/>
       <c r="B22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="4"/>
+      <c r="I22" s="1"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
+      <c r="K22" s="1"/>
       <c r="L22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="4"/>
+      <c r="A23" s="1"/>
       <c r="B23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="4"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
+      <c r="I23" s="1"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
+      <c r="K23" s="1"/>
       <c r="L23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="4"/>
+      <c r="A24" s="1"/>
       <c r="B24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="4"/>
+      <c r="E24" s="1"/>
       <c r="F24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
+      <c r="K24" s="1"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="4"/>
+      <c r="A25" s="1"/>
       <c r="B25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="4"/>
+      <c r="I25" s="1"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
+      <c r="K25" s="1"/>
       <c r="L25" s="3"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="4"/>
+      <c r="A26" s="1"/>
       <c r="B26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="1"/>
       <c r="F26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="4"/>
+      <c r="I26" s="1"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
+      <c r="K26" s="1"/>
       <c r="L26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="4"/>
+      <c r="A27" s="1"/>
       <c r="B27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="4"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="4"/>
+      <c r="I27" s="1"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
+      <c r="K27" s="1"/>
       <c r="L27" s="3"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="4"/>
+      <c r="A28" s="1"/>
       <c r="B28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="4"/>
+      <c r="I28" s="1"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
+      <c r="K28" s="1"/>
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="4"/>
+      <c r="A29" s="1"/>
       <c r="B29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="1"/>
       <c r="F29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="4"/>
+      <c r="I29" s="1"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
+      <c r="K29" s="1"/>
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="4"/>
+      <c r="A30" s="1"/>
       <c r="B30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="4"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
+      <c r="K30" s="1"/>
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="4"/>
+      <c r="A31" s="1"/>
       <c r="B31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="4"/>
+      <c r="I31" s="1"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
+      <c r="K31" s="1"/>
       <c r="L31" s="3"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="1"/>
       <c r="B32" s="3"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="1"/>
       <c r="F32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="4"/>
+      <c r="I32" s="1"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
+      <c r="K32" s="1"/>
       <c r="L32" s="3"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="4"/>
+      <c r="A33" s="1"/>
       <c r="B33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="1"/>
       <c r="F33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="4"/>
+      <c r="I33" s="1"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="4"/>
+      <c r="K33" s="1"/>
       <c r="L33" s="3"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="4"/>
+      <c r="A34" s="1"/>
       <c r="B34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="4"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="4"/>
+      <c r="I34" s="1"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="4"/>
+      <c r="K34" s="1"/>
       <c r="L34" s="3"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="4"/>
+      <c r="A35" s="1"/>
       <c r="B35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="4"/>
+      <c r="I35" s="1"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="4"/>
+      <c r="K35" s="1"/>
       <c r="L35" s="3"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="1"/>
       <c r="B36" s="3"/>
       <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="3"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="1"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="4"/>
+      <c r="K36" s="1"/>
       <c r="L36" s="3"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="4"/>
+      <c r="A37" s="1"/>
       <c r="B37" s="3"/>
       <c r="D37" s="3"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="4"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="4"/>
+      <c r="K37" s="1"/>
       <c r="L37" s="3"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="1"/>
       <c r="B38" s="3"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="1"/>
       <c r="F38" s="3"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="4"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="4"/>
+      <c r="K38" s="1"/>
       <c r="L38" s="3"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="1"/>
       <c r="B39" s="3"/>
       <c r="D39" s="3"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="1"/>
       <c r="F39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="4"/>
+      <c r="I39" s="1"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="4"/>
+      <c r="K39" s="1"/>
       <c r="L39" s="3"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="4"/>
+      <c r="A40" s="1"/>
       <c r="B40" s="3"/>
       <c r="D40" s="3"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="1"/>
       <c r="F40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="4"/>
+      <c r="I40" s="1"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="4"/>
+      <c r="K40" s="1"/>
       <c r="L40" s="3"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="4"/>
+      <c r="A41" s="1"/>
       <c r="B41" s="3"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="4"/>
+      <c r="E41" s="1"/>
       <c r="F41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="4"/>
+      <c r="I41" s="1"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="4"/>
+      <c r="K41" s="1"/>
       <c r="L41" s="3"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="4"/>
+      <c r="A42" s="1"/>
       <c r="B42" s="3"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="1"/>
       <c r="F42" s="3"/>
       <c r="H42" s="3"/>
-      <c r="I42" s="4"/>
+      <c r="I42" s="1"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="4"/>
+      <c r="K42" s="1"/>
       <c r="L42" s="3"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="4"/>
+      <c r="A43" s="1"/>
       <c r="B43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="4"/>
+      <c r="E43" s="1"/>
       <c r="F43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="4"/>
+      <c r="I43" s="1"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="4"/>
+      <c r="K43" s="1"/>
       <c r="L43" s="3"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="4"/>
+      <c r="A44" s="1"/>
       <c r="B44" s="3"/>
       <c r="D44" s="3"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="4"/>
+      <c r="I44" s="1"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="4"/>
+      <c r="K44" s="1"/>
       <c r="L44" s="3"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="4"/>
+      <c r="A45" s="1"/>
       <c r="B45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="1"/>
       <c r="F45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="4"/>
+      <c r="I45" s="1"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="4"/>
+      <c r="K45" s="1"/>
       <c r="L45" s="3"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="4"/>
+      <c r="A46" s="1"/>
       <c r="B46" s="3"/>
       <c r="D46" s="3"/>
-      <c r="E46" s="4"/>
+      <c r="E46" s="1"/>
       <c r="F46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="K46" s="4"/>
+      <c r="K46" s="1"/>
       <c r="L46" s="3"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="4"/>
+      <c r="A47" s="1"/>
       <c r="B47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="4"/>
+      <c r="E47" s="1"/>
       <c r="F47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="K47" s="4"/>
+      <c r="K47" s="1"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="4"/>
+      <c r="A48" s="1"/>
       <c r="B48" s="3"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="4"/>
+      <c r="E48" s="1"/>
       <c r="F48" s="3"/>
       <c r="H48" s="3"/>
-      <c r="K48" s="4"/>
+      <c r="K48" s="1"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="4"/>
+      <c r="A49" s="1"/>
       <c r="B49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="1"/>
       <c r="F49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="K49" s="4"/>
+      <c r="K49" s="1"/>
       <c r="L49" s="3"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="4"/>
+      <c r="A50" s="1"/>
       <c r="B50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="4"/>
+      <c r="E50" s="1"/>
       <c r="F50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="K50" s="4"/>
+      <c r="K50" s="1"/>
       <c r="L50" s="3"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="4"/>
+      <c r="A51" s="1"/>
       <c r="B51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="1"/>
       <c r="F51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="K51" s="4"/>
+      <c r="K51" s="1"/>
       <c r="L51" s="3"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="4"/>
+      <c r="A52" s="1"/>
       <c r="B52" s="3"/>
-      <c r="E52" s="4"/>
+      <c r="E52" s="1"/>
       <c r="F52" s="3"/>
       <c r="H52" s="3"/>
-      <c r="K52" s="4"/>
+      <c r="K52" s="1"/>
       <c r="L52" s="3"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="4"/>
+      <c r="A53" s="1"/>
       <c r="B53" s="3"/>
-      <c r="E53" s="4"/>
+      <c r="E53" s="1"/>
       <c r="F53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="K53" s="4"/>
+      <c r="K53" s="1"/>
       <c r="L53" s="3"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="4"/>
+      <c r="A54" s="1"/>
       <c r="B54" s="3"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="1"/>
       <c r="F54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="K54" s="4"/>
+      <c r="K54" s="1"/>
       <c r="L54" s="3"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="4"/>
+      <c r="A55" s="1"/>
       <c r="B55" s="3"/>
-      <c r="E55" s="4"/>
+      <c r="E55" s="1"/>
       <c r="F55" s="3"/>
       <c r="H55" s="3"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="4"/>
+      <c r="A56" s="1"/>
       <c r="B56" s="3"/>
-      <c r="E56" s="4"/>
+      <c r="E56" s="1"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="4"/>
+      <c r="A57" s="1"/>
       <c r="B57" s="3"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="1"/>
       <c r="F57" s="3"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="4"/>
+      <c r="A58" s="1"/>
       <c r="B58" s="3"/>
-      <c r="E58" s="4"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="3"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="4"/>
+      <c r="A59" s="1"/>
       <c r="B59" s="3"/>
-      <c r="E59" s="4"/>
+      <c r="E59" s="1"/>
       <c r="F59" s="3"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="4"/>
+      <c r="A60" s="1"/>
       <c r="B60" s="3"/>
-      <c r="E60" s="4"/>
+      <c r="E60" s="1"/>
       <c r="F60" s="3"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="4"/>
+      <c r="A61" s="1"/>
       <c r="B61" s="3"/>
-      <c r="E61" s="4"/>
+      <c r="E61" s="1"/>
       <c r="F61" s="3"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="4"/>
+      <c r="A62" s="1"/>
       <c r="B62" s="3"/>
-      <c r="E62" s="4"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="3"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="4"/>
+      <c r="A63" s="1"/>
       <c r="B63" s="3"/>
-      <c r="E63" s="4"/>
+      <c r="E63" s="1"/>
       <c r="F63" s="3"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="4"/>
+      <c r="A64" s="1"/>
       <c r="B64" s="3"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="1"/>
       <c r="F64" s="3"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="4"/>
+      <c r="A65" s="1"/>
       <c r="B65" s="3"/>
-      <c r="E65" s="4"/>
+      <c r="E65" s="1"/>
       <c r="F65" s="3"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="4"/>
+      <c r="A66" s="1"/>
       <c r="B66" s="3"/>
-      <c r="E66" s="4"/>
+      <c r="E66" s="1"/>
       <c r="F66" s="3"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="4"/>
+      <c r="A67" s="1"/>
       <c r="B67" s="3"/>
-      <c r="E67" s="4"/>
+      <c r="E67" s="1"/>
       <c r="F67" s="3"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="4"/>
+      <c r="A68" s="1"/>
       <c r="B68" s="3"/>
-      <c r="E68" s="4"/>
+      <c r="E68" s="1"/>
       <c r="F68" s="3"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="4"/>
+      <c r="A69" s="1"/>
       <c r="B69" s="3"/>
-      <c r="E69" s="4"/>
+      <c r="E69" s="1"/>
       <c r="F69" s="3"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="4"/>
+      <c r="A70" s="1"/>
       <c r="B70" s="3"/>
-      <c r="E70" s="4"/>
+      <c r="E70" s="1"/>
       <c r="F70" s="3"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="4"/>
+      <c r="A71" s="1"/>
       <c r="B71" s="3"/>
-      <c r="E71" s="4"/>
+      <c r="E71" s="1"/>
       <c r="F71" s="3"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="4"/>
+      <c r="A72" s="1"/>
       <c r="B72" s="3"/>
-      <c r="E72" s="4"/>
+      <c r="E72" s="1"/>
       <c r="F72" s="3"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="4"/>
+      <c r="A73" s="1"/>
       <c r="B73" s="3"/>
-      <c r="E73" s="4"/>
+      <c r="E73" s="1"/>
       <c r="F73" s="3"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="4"/>
+      <c r="A74" s="1"/>
       <c r="B74" s="3"/>
-      <c r="E74" s="4"/>
+      <c r="E74" s="1"/>
       <c r="F74" s="3"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="4"/>
+      <c r="A75" s="1"/>
       <c r="B75" s="3"/>
-      <c r="E75" s="4"/>
+      <c r="E75" s="1"/>
       <c r="F75" s="3"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="4"/>
+      <c r="A76" s="1"/>
       <c r="B76" s="3"/>
-      <c r="E76" s="4"/>
+      <c r="E76" s="1"/>
       <c r="F76" s="3"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="4"/>
+      <c r="A77" s="1"/>
       <c r="B77" s="3"/>
-      <c r="E77" s="4"/>
+      <c r="E77" s="1"/>
       <c r="F77" s="3"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="4"/>
+      <c r="A78" s="1"/>
       <c r="B78" s="3"/>
-      <c r="E78" s="4"/>
+      <c r="E78" s="1"/>
       <c r="F78" s="3"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="4"/>
+      <c r="A79" s="1"/>
       <c r="B79" s="3"/>
-      <c r="E79" s="4"/>
+      <c r="E79" s="1"/>
       <c r="F79" s="3"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="4"/>
+      <c r="A80" s="1"/>
       <c r="B80" s="3"/>
-      <c r="E80" s="4"/>
+      <c r="E80" s="1"/>
       <c r="F80" s="3"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="4"/>
+      <c r="A81" s="1"/>
       <c r="B81" s="3"/>
-      <c r="E81" s="4"/>
+      <c r="E81" s="1"/>
       <c r="F81" s="3"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="4"/>
+      <c r="A82" s="1"/>
       <c r="B82" s="3"/>
-      <c r="E82" s="4"/>
+      <c r="E82" s="1"/>
       <c r="F82" s="3"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="4"/>
+      <c r="A83" s="1"/>
       <c r="B83" s="3"/>
-      <c r="E83" s="4"/>
+      <c r="E83" s="1"/>
       <c r="F83" s="3"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="4"/>
+      <c r="A84" s="1"/>
       <c r="B84" s="3"/>
-      <c r="E84" s="4"/>
+      <c r="E84" s="1"/>
       <c r="F84" s="3"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="4"/>
+      <c r="A85" s="1"/>
       <c r="B85" s="3"/>
-      <c r="E85" s="4"/>
+      <c r="E85" s="1"/>
       <c r="F85" s="3"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="4"/>
+      <c r="A86" s="1"/>
       <c r="B86" s="3"/>
-      <c r="E86" s="4"/>
+      <c r="E86" s="1"/>
       <c r="F86" s="3"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="4"/>
+      <c r="A87" s="1"/>
       <c r="B87" s="3"/>
-      <c r="E87" s="4"/>
+      <c r="E87" s="1"/>
       <c r="F87" s="3"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="4"/>
+      <c r="A88" s="1"/>
       <c r="B88" s="3"/>
-      <c r="E88" s="4"/>
+      <c r="E88" s="1"/>
       <c r="F88" s="3"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="4"/>
+      <c r="A89" s="1"/>
       <c r="B89" s="3"/>
-      <c r="E89" s="4"/>
+      <c r="E89" s="1"/>
       <c r="F89" s="3"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="4"/>
+      <c r="A90" s="1"/>
       <c r="B90" s="3"/>
-      <c r="E90" s="4"/>
+      <c r="E90" s="1"/>
       <c r="F90" s="3"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="4"/>
+      <c r="A91" s="1"/>
       <c r="B91" s="3"/>
-      <c r="E91" s="4"/>
+      <c r="E91" s="1"/>
       <c r="F91" s="3"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="4"/>
+      <c r="A92" s="1"/>
       <c r="B92" s="3"/>
-      <c r="E92" s="4"/>
+      <c r="E92" s="1"/>
       <c r="F92" s="3"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="4"/>
+      <c r="A93" s="1"/>
       <c r="B93" s="3"/>
-      <c r="E93" s="4"/>
+      <c r="E93" s="1"/>
       <c r="F93" s="3"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="4"/>
+      <c r="A94" s="1"/>
       <c r="B94" s="3"/>
-      <c r="E94" s="4"/>
+      <c r="E94" s="1"/>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="4"/>
+      <c r="A95" s="1"/>
       <c r="B95" s="3"/>
-      <c r="E95" s="4"/>
+      <c r="E95" s="1"/>
       <c r="F95" s="3"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="4"/>
+      <c r="A96" s="1"/>
       <c r="B96" s="3"/>
-      <c r="E96" s="4"/>
+      <c r="E96" s="1"/>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="4"/>
+      <c r="A97" s="1"/>
       <c r="B97" s="3"/>
-      <c r="E97" s="4"/>
+      <c r="E97" s="1"/>
       <c r="F97" s="3"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="4"/>
+      <c r="A98" s="1"/>
       <c r="B98" s="3"/>
-      <c r="E98" s="4"/>
+      <c r="E98" s="1"/>
       <c r="F98" s="3"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="4"/>
+      <c r="A99" s="1"/>
       <c r="B99" s="3"/>
-      <c r="E99" s="4"/>
+      <c r="E99" s="1"/>
       <c r="F99" s="3"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="4"/>
+      <c r="A100" s="1"/>
       <c r="B100" s="3"/>
-      <c r="E100" s="4"/>
+      <c r="E100" s="1"/>
       <c r="F100" s="3"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="4"/>
+      <c r="A101" s="1"/>
       <c r="B101" s="3"/>
-      <c r="E101" s="4"/>
+      <c r="E101" s="1"/>
       <c r="F101" s="3"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="4"/>
+      <c r="A102" s="1"/>
       <c r="B102" s="3"/>
-      <c r="E102" s="4"/>
+      <c r="E102" s="1"/>
       <c r="F102" s="3"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="4"/>
+      <c r="A103" s="1"/>
       <c r="B103" s="3"/>
-      <c r="E103" s="4"/>
+      <c r="E103" s="1"/>
       <c r="F103" s="3"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="4"/>
+      <c r="A104" s="1"/>
       <c r="B104" s="3"/>
-      <c r="E104" s="4"/>
+      <c r="E104" s="1"/>
       <c r="F104" s="3"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="4"/>
+      <c r="A105" s="1"/>
       <c r="B105" s="3"/>
-      <c r="E105" s="4"/>
+      <c r="E105" s="1"/>
       <c r="F105" s="3"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="4"/>
+      <c r="A106" s="1"/>
       <c r="B106" s="3"/>
-      <c r="E106" s="4"/>
+      <c r="E106" s="1"/>
       <c r="F106" s="3"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="4"/>
+      <c r="A107" s="1"/>
       <c r="B107" s="3"/>
-      <c r="E107" s="4"/>
+      <c r="E107" s="1"/>
       <c r="F107" s="3"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="4"/>
+      <c r="A108" s="1"/>
       <c r="B108" s="3"/>
-      <c r="E108" s="4"/>
+      <c r="E108" s="1"/>
       <c r="F108" s="3"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="4"/>
+      <c r="A109" s="1"/>
       <c r="B109" s="3"/>
-      <c r="E109" s="4"/>
+      <c r="E109" s="1"/>
       <c r="F109" s="3"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="4"/>
+      <c r="A110" s="1"/>
       <c r="B110" s="3"/>
-      <c r="E110" s="4"/>
+      <c r="E110" s="1"/>
       <c r="F110" s="3"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="4"/>
+      <c r="A111" s="1"/>
       <c r="B111" s="3"/>
-      <c r="E111" s="4"/>
+      <c r="E111" s="1"/>
       <c r="F111" s="3"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="4"/>
+      <c r="A112" s="1"/>
       <c r="B112" s="3"/>
-      <c r="E112" s="4"/>
+      <c r="E112" s="1"/>
       <c r="F112" s="3"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="4"/>
+      <c r="A113" s="1"/>
       <c r="B113" s="3"/>
-      <c r="E113" s="4"/>
+      <c r="E113" s="1"/>
       <c r="F113" s="3"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="4"/>
+      <c r="A114" s="1"/>
       <c r="B114" s="3"/>
-      <c r="E114" s="4"/>
+      <c r="E114" s="1"/>
       <c r="F114" s="3"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="4"/>
+      <c r="A115" s="1"/>
       <c r="B115" s="3"/>
-      <c r="E115" s="4"/>
+      <c r="E115" s="1"/>
       <c r="F115" s="3"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="4"/>
+      <c r="A116" s="1"/>
       <c r="B116" s="3"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="4"/>
+      <c r="A117" s="1"/>
       <c r="B117" s="3"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="4"/>
+      <c r="A118" s="1"/>
       <c r="B118" s="3"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="4"/>
+      <c r="A119" s="1"/>
       <c r="B119" s="3"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="4"/>
+      <c r="A120" s="1"/>
       <c r="B120" s="3"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="4"/>
+      <c r="A121" s="1"/>
       <c r="B121" s="3"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="4"/>
+      <c r="A122" s="1"/>
       <c r="B122" s="3"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="4"/>
+      <c r="A123" s="1"/>
       <c r="B123" s="3"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="4"/>
+      <c r="A124" s="1"/>
       <c r="B124" s="3"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="4"/>
+      <c r="A125" s="1"/>
       <c r="B125" s="3"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="4"/>
+      <c r="A126" s="1"/>
       <c r="B126" s="3"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="4"/>
+      <c r="A127" s="1"/>
       <c r="B127" s="3"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="4"/>
+      <c r="A128" s="1"/>
       <c r="B128" s="3"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="4"/>
+      <c r="A129" s="1"/>
       <c r="B129" s="3"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="4"/>
+      <c r="A130" s="1"/>
       <c r="B130" s="3"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="4"/>
+      <c r="A131" s="1"/>
       <c r="B131" s="3"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="4"/>
+      <c r="A132" s="1"/>
       <c r="B132" s="3"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="4"/>
+      <c r="A133" s="1"/>
       <c r="B133" s="3"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="4"/>
+      <c r="A134" s="1"/>
       <c r="B134" s="3"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="4"/>
+      <c r="A135" s="1"/>
       <c r="B135" s="3"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="4"/>
+      <c r="A136" s="1"/>
       <c r="B136" s="3"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="4"/>
+      <c r="A137" s="1"/>
       <c r="B137" s="3"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="4"/>
+      <c r="A138" s="1"/>
       <c r="B138" s="3"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="4"/>
+      <c r="A139" s="1"/>
       <c r="B139" s="3"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="4"/>
+      <c r="A140" s="1"/>
       <c r="B140" s="3"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="4"/>
+      <c r="A141" s="1"/>
       <c r="B141" s="3"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="4"/>
+      <c r="A142" s="1"/>
       <c r="B142" s="3"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="4"/>
+      <c r="A143" s="1"/>
       <c r="B143" s="3"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="4"/>
+      <c r="A144" s="1"/>
       <c r="B144" s="3"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="4"/>
+      <c r="A145" s="1"/>
       <c r="B145" s="3"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="4"/>
+      <c r="A146" s="1"/>
       <c r="B146" s="3"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="4"/>
+      <c r="A147" s="1"/>
       <c r="B147" s="3"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="4"/>
+      <c r="A148" s="1"/>
       <c r="B148" s="3"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="4"/>
+      <c r="A149" s="1"/>
       <c r="B149" s="3"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="4"/>
+      <c r="A150" s="1"/>
       <c r="B150" s="3"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="4"/>
+      <c r="A151" s="1"/>
       <c r="B151" s="3"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="4"/>
+      <c r="A152" s="1"/>
       <c r="B152" s="3"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="4"/>
+      <c r="A153" s="1"/>
       <c r="B153" s="3"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="4"/>
+      <c r="A154" s="1"/>
       <c r="B154" s="3"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="4"/>
+      <c r="A155" s="1"/>
       <c r="B155" s="3"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="4"/>
+      <c r="A156" s="1"/>
       <c r="B156" s="3"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="4"/>
+      <c r="A157" s="1"/>
       <c r="B157" s="3"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="4"/>
+      <c r="A158" s="1"/>
       <c r="B158" s="3"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="4"/>
+      <c r="A159" s="1"/>
       <c r="B159" s="3"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="4"/>
+      <c r="A160" s="1"/>
       <c r="B160" s="3"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="4"/>
+      <c r="A161" s="1"/>
       <c r="B161" s="3"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="4"/>
+      <c r="A162" s="1"/>
       <c r="B162" s="3"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="4"/>
+      <c r="A163" s="1"/>
       <c r="B163" s="3"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="4"/>
+      <c r="A164" s="1"/>
       <c r="B164" s="3"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="4"/>
+      <c r="A165" s="1"/>
       <c r="B165" s="3"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="4"/>
+      <c r="A166" s="1"/>
       <c r="B166" s="3"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="4"/>
+      <c r="A167" s="1"/>
       <c r="B167" s="3"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="4"/>
+      <c r="A168" s="1"/>
       <c r="B168" s="3"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="4"/>
+      <c r="A169" s="1"/>
       <c r="B169" s="3"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="4"/>
+      <c r="A170" s="1"/>
       <c r="B170" s="3"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="4"/>
+      <c r="A171" s="1"/>
       <c r="B171" s="3"/>
     </row>
     <row r="172" ht="14.25" customHeight="1"/>
@@ -7256,1240 +7201,1235 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="37.29"/>
-    <col customWidth="1" min="2" max="2" width="29.57"/>
-    <col customWidth="1" min="3" max="3" width="24.57"/>
-    <col customWidth="1" min="4" max="4" width="27.57"/>
-    <col customWidth="1" min="5" max="5" width="25.29"/>
-    <col customWidth="1" min="6" max="6" width="33.57"/>
+    <col min="1" max="1" width="37.29" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="24.57" customWidth="1"/>
+    <col min="4" max="4" width="27.57" customWidth="1"/>
+    <col min="5" max="5" width="25.29" customWidth="1"/>
+    <col min="6" max="6" width="33.57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="4"/>
+      <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
+      <c r="E1" s="1"/>
       <c r="F1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="4"/>
+      <c r="K1" s="1"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4"/>
+      <c r="A2" s="1"/>
       <c r="B2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
+      <c r="I2" s="1"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4"/>
+      <c r="A3" s="1"/>
       <c r="B3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
+      <c r="I3" s="1"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
+      <c r="K3" s="1"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4"/>
+      <c r="A4" s="1"/>
       <c r="B4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="4"/>
+      <c r="I4" s="1"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
+      <c r="K4" s="1"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4"/>
+      <c r="A5" s="1"/>
       <c r="B5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
+      <c r="E5" s="1"/>
       <c r="F5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
+      <c r="K5" s="1"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="4"/>
+      <c r="A6" s="1"/>
       <c r="B6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="1"/>
       <c r="F6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="1"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
+      <c r="K6" s="1"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="4"/>
+      <c r="A7" s="1"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="1"/>
       <c r="F7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
+      <c r="I7" s="1"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="1"/>
       <c r="L7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="4"/>
+      <c r="A8" s="1"/>
       <c r="B8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="1"/>
       <c r="F8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="4"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
+      <c r="K8" s="1"/>
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="4"/>
+      <c r="A9" s="1"/>
       <c r="B9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="4"/>
+      <c r="I9" s="1"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
+      <c r="K9" s="1"/>
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="4"/>
+      <c r="A10" s="1"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
+      <c r="K10" s="1"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="4"/>
+      <c r="A11" s="1"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
+      <c r="E11" s="1"/>
       <c r="F11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
+      <c r="I11" s="1"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
+      <c r="K11" s="1"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="4"/>
+      <c r="A12" s="1"/>
       <c r="B12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
+      <c r="I12" s="1"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
+      <c r="K12" s="1"/>
       <c r="L12" s="3"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="4"/>
+      <c r="A13" s="1"/>
       <c r="B13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
+      <c r="I13" s="1"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
+      <c r="K13" s="1"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="4"/>
+      <c r="A14" s="1"/>
       <c r="B14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="4"/>
+      <c r="I14" s="1"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
+      <c r="K14" s="1"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="4"/>
+      <c r="A15" s="1"/>
       <c r="B15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="1"/>
       <c r="F15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="4"/>
+      <c r="I15" s="1"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
+      <c r="K15" s="1"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="4"/>
+      <c r="A16" s="1"/>
       <c r="B16" s="3"/>
       <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="1"/>
       <c r="F16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="1"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
+      <c r="K16" s="1"/>
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="4"/>
+      <c r="A17" s="1"/>
       <c r="B17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="1"/>
       <c r="F17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="4"/>
+      <c r="I17" s="1"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
+      <c r="K17" s="1"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="4"/>
+      <c r="A18" s="1"/>
       <c r="B18" s="3"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="1"/>
       <c r="F18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="4"/>
+      <c r="I18" s="1"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
+      <c r="K18" s="1"/>
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="4"/>
+      <c r="A19" s="1"/>
       <c r="B19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="4"/>
+      <c r="E19" s="1"/>
       <c r="F19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="4"/>
+      <c r="I19" s="1"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="4"/>
+      <c r="A20" s="1"/>
       <c r="B20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="4"/>
+      <c r="E20" s="1"/>
       <c r="F20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="4"/>
+      <c r="I20" s="1"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="4"/>
+      <c r="A21" s="1"/>
       <c r="B21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="4"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="4"/>
+      <c r="I21" s="1"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="3"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="4"/>
+      <c r="A22" s="1"/>
       <c r="B22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="4"/>
+      <c r="I22" s="1"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
+      <c r="K22" s="1"/>
       <c r="L22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="4"/>
+      <c r="A23" s="1"/>
       <c r="B23" s="3"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="4"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
+      <c r="I23" s="1"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
+      <c r="K23" s="1"/>
       <c r="L23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="4"/>
+      <c r="A24" s="1"/>
       <c r="B24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="4"/>
+      <c r="E24" s="1"/>
       <c r="F24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
+      <c r="K24" s="1"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="4"/>
+      <c r="A25" s="1"/>
       <c r="B25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="4"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="4"/>
+      <c r="I25" s="1"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
+      <c r="K25" s="1"/>
       <c r="L25" s="3"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="4"/>
+      <c r="A26" s="1"/>
       <c r="B26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="4"/>
+      <c r="E26" s="1"/>
       <c r="F26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="4"/>
+      <c r="I26" s="1"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
+      <c r="K26" s="1"/>
       <c r="L26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="4"/>
+      <c r="A27" s="1"/>
       <c r="B27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="4"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="4"/>
+      <c r="I27" s="1"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
+      <c r="K27" s="1"/>
       <c r="L27" s="3"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="4"/>
+      <c r="A28" s="1"/>
       <c r="B28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="4"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="4"/>
+      <c r="I28" s="1"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
+      <c r="K28" s="1"/>
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="4"/>
+      <c r="A29" s="1"/>
       <c r="B29" s="3"/>
       <c r="D29" s="3"/>
-      <c r="E29" s="4"/>
+      <c r="E29" s="1"/>
       <c r="F29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="4"/>
+      <c r="I29" s="1"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
+      <c r="K29" s="1"/>
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="4"/>
+      <c r="A30" s="1"/>
       <c r="B30" s="3"/>
       <c r="D30" s="3"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="4"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
+      <c r="K30" s="1"/>
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="4"/>
+      <c r="A31" s="1"/>
       <c r="B31" s="3"/>
       <c r="D31" s="3"/>
-      <c r="E31" s="4"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="4"/>
+      <c r="I31" s="1"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
+      <c r="K31" s="1"/>
       <c r="L31" s="3"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="4"/>
+      <c r="A32" s="1"/>
       <c r="B32" s="3"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="1"/>
       <c r="F32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="4"/>
+      <c r="I32" s="1"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
+      <c r="K32" s="1"/>
       <c r="L32" s="3"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="4"/>
+      <c r="A33" s="1"/>
       <c r="B33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="1"/>
       <c r="F33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="4"/>
+      <c r="I33" s="1"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="4"/>
+      <c r="K33" s="1"/>
       <c r="L33" s="3"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="4"/>
+      <c r="A34" s="1"/>
       <c r="B34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="4"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="4"/>
+      <c r="I34" s="1"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="4"/>
+      <c r="K34" s="1"/>
       <c r="L34" s="3"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="4"/>
+      <c r="A35" s="1"/>
       <c r="B35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="3"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="4"/>
+      <c r="I35" s="1"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="4"/>
+      <c r="K35" s="1"/>
       <c r="L35" s="3"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="4"/>
+      <c r="A36" s="1"/>
       <c r="B36" s="3"/>
       <c r="D36" s="3"/>
-      <c r="E36" s="4"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="3"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="1"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="4"/>
+      <c r="K36" s="1"/>
       <c r="L36" s="3"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="4"/>
+      <c r="A37" s="1"/>
       <c r="B37" s="3"/>
       <c r="D37" s="3"/>
-      <c r="E37" s="4"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="3"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="4"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="4"/>
+      <c r="K37" s="1"/>
       <c r="L37" s="3"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="4"/>
+      <c r="A38" s="1"/>
       <c r="B38" s="3"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="4"/>
+      <c r="E38" s="1"/>
       <c r="F38" s="3"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="4"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="4"/>
+      <c r="K38" s="1"/>
       <c r="L38" s="3"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="4"/>
+      <c r="A39" s="1"/>
       <c r="B39" s="3"/>
       <c r="D39" s="3"/>
-      <c r="E39" s="4"/>
+      <c r="E39" s="1"/>
       <c r="F39" s="3"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="4"/>
+      <c r="I39" s="1"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="4"/>
+      <c r="K39" s="1"/>
       <c r="L39" s="3"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="4"/>
+      <c r="A40" s="1"/>
       <c r="B40" s="3"/>
       <c r="D40" s="3"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="1"/>
       <c r="F40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="4"/>
+      <c r="I40" s="1"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="4"/>
+      <c r="K40" s="1"/>
       <c r="L40" s="3"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="4"/>
+      <c r="A41" s="1"/>
       <c r="B41" s="3"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="4"/>
+      <c r="E41" s="1"/>
       <c r="F41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="4"/>
+      <c r="I41" s="1"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="4"/>
+      <c r="K41" s="1"/>
       <c r="L41" s="3"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="4"/>
+      <c r="A42" s="1"/>
       <c r="B42" s="3"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="4"/>
+      <c r="E42" s="1"/>
       <c r="F42" s="3"/>
       <c r="H42" s="3"/>
-      <c r="I42" s="4"/>
+      <c r="I42" s="1"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="4"/>
+      <c r="K42" s="1"/>
       <c r="L42" s="3"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="4"/>
+      <c r="A43" s="1"/>
       <c r="B43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="4"/>
+      <c r="E43" s="1"/>
       <c r="F43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="4"/>
+      <c r="I43" s="1"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="4"/>
+      <c r="K43" s="1"/>
       <c r="L43" s="3"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="4"/>
+      <c r="A44" s="1"/>
       <c r="B44" s="3"/>
       <c r="D44" s="3"/>
-      <c r="E44" s="4"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="4"/>
+      <c r="I44" s="1"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="4"/>
+      <c r="K44" s="1"/>
       <c r="L44" s="3"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="4"/>
+      <c r="A45" s="1"/>
       <c r="B45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="4"/>
+      <c r="E45" s="1"/>
       <c r="F45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="4"/>
+      <c r="I45" s="1"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="4"/>
+      <c r="K45" s="1"/>
       <c r="L45" s="3"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="4"/>
+      <c r="A46" s="1"/>
       <c r="B46" s="3"/>
       <c r="D46" s="3"/>
-      <c r="E46" s="4"/>
+      <c r="E46" s="1"/>
       <c r="F46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="K46" s="4"/>
+      <c r="K46" s="1"/>
       <c r="L46" s="3"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="4"/>
+      <c r="A47" s="1"/>
       <c r="B47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="4"/>
+      <c r="E47" s="1"/>
       <c r="F47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="K47" s="4"/>
+      <c r="K47" s="1"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="4"/>
+      <c r="A48" s="1"/>
       <c r="B48" s="3"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="4"/>
+      <c r="E48" s="1"/>
       <c r="F48" s="3"/>
       <c r="H48" s="3"/>
-      <c r="K48" s="4"/>
+      <c r="K48" s="1"/>
       <c r="L48" s="3"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="4"/>
+      <c r="A49" s="1"/>
       <c r="B49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="4"/>
+      <c r="E49" s="1"/>
       <c r="F49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="K49" s="4"/>
+      <c r="K49" s="1"/>
       <c r="L49" s="3"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" s="4"/>
+      <c r="A50" s="1"/>
       <c r="B50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="4"/>
+      <c r="E50" s="1"/>
       <c r="F50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="K50" s="4"/>
+      <c r="K50" s="1"/>
       <c r="L50" s="3"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="4"/>
+      <c r="A51" s="1"/>
       <c r="B51" s="3"/>
       <c r="D51" s="3"/>
-      <c r="E51" s="4"/>
+      <c r="E51" s="1"/>
       <c r="F51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="K51" s="4"/>
+      <c r="K51" s="1"/>
       <c r="L51" s="3"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="4"/>
+      <c r="A52" s="1"/>
       <c r="B52" s="3"/>
-      <c r="E52" s="4"/>
+      <c r="E52" s="1"/>
       <c r="F52" s="3"/>
       <c r="H52" s="3"/>
-      <c r="K52" s="4"/>
+      <c r="K52" s="1"/>
       <c r="L52" s="3"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="4"/>
+      <c r="A53" s="1"/>
       <c r="B53" s="3"/>
-      <c r="E53" s="4"/>
+      <c r="E53" s="1"/>
       <c r="F53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="K53" s="4"/>
+      <c r="K53" s="1"/>
       <c r="L53" s="3"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="4"/>
+      <c r="A54" s="1"/>
       <c r="B54" s="3"/>
-      <c r="E54" s="4"/>
+      <c r="E54" s="1"/>
       <c r="F54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="K54" s="4"/>
+      <c r="K54" s="1"/>
       <c r="L54" s="3"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" s="4"/>
+      <c r="A55" s="1"/>
       <c r="B55" s="3"/>
-      <c r="E55" s="4"/>
+      <c r="E55" s="1"/>
       <c r="F55" s="3"/>
       <c r="H55" s="3"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" s="4"/>
+      <c r="A56" s="1"/>
       <c r="B56" s="3"/>
-      <c r="E56" s="4"/>
+      <c r="E56" s="1"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="4"/>
+      <c r="A57" s="1"/>
       <c r="B57" s="3"/>
-      <c r="E57" s="4"/>
+      <c r="E57" s="1"/>
       <c r="F57" s="3"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" s="4"/>
+      <c r="A58" s="1"/>
       <c r="B58" s="3"/>
-      <c r="E58" s="4"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="3"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" s="4"/>
+      <c r="A59" s="1"/>
       <c r="B59" s="3"/>
-      <c r="E59" s="4"/>
+      <c r="E59" s="1"/>
       <c r="F59" s="3"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="4"/>
+      <c r="A60" s="1"/>
       <c r="B60" s="3"/>
-      <c r="E60" s="4"/>
+      <c r="E60" s="1"/>
       <c r="F60" s="3"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="4"/>
+      <c r="A61" s="1"/>
       <c r="B61" s="3"/>
-      <c r="E61" s="4"/>
+      <c r="E61" s="1"/>
       <c r="F61" s="3"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="4"/>
+      <c r="A62" s="1"/>
       <c r="B62" s="3"/>
-      <c r="E62" s="4"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="3"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" s="4"/>
+      <c r="A63" s="1"/>
       <c r="B63" s="3"/>
-      <c r="E63" s="4"/>
+      <c r="E63" s="1"/>
       <c r="F63" s="3"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="4"/>
+      <c r="A64" s="1"/>
       <c r="B64" s="3"/>
-      <c r="E64" s="4"/>
+      <c r="E64" s="1"/>
       <c r="F64" s="3"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="4"/>
+      <c r="A65" s="1"/>
       <c r="B65" s="3"/>
-      <c r="E65" s="4"/>
+      <c r="E65" s="1"/>
       <c r="F65" s="3"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="4"/>
+      <c r="A66" s="1"/>
       <c r="B66" s="3"/>
-      <c r="E66" s="4"/>
+      <c r="E66" s="1"/>
       <c r="F66" s="3"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="4"/>
+      <c r="A67" s="1"/>
       <c r="B67" s="3"/>
-      <c r="E67" s="4"/>
+      <c r="E67" s="1"/>
       <c r="F67" s="3"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="4"/>
+      <c r="A68" s="1"/>
       <c r="B68" s="3"/>
-      <c r="E68" s="4"/>
+      <c r="E68" s="1"/>
       <c r="F68" s="3"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
-      <c r="A69" s="4"/>
+      <c r="A69" s="1"/>
       <c r="B69" s="3"/>
-      <c r="E69" s="4"/>
+      <c r="E69" s="1"/>
       <c r="F69" s="3"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="4"/>
+      <c r="A70" s="1"/>
       <c r="B70" s="3"/>
-      <c r="E70" s="4"/>
+      <c r="E70" s="1"/>
       <c r="F70" s="3"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="4"/>
+      <c r="A71" s="1"/>
       <c r="B71" s="3"/>
-      <c r="E71" s="4"/>
+      <c r="E71" s="1"/>
       <c r="F71" s="3"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="4"/>
+      <c r="A72" s="1"/>
       <c r="B72" s="3"/>
-      <c r="E72" s="4"/>
+      <c r="E72" s="1"/>
       <c r="F72" s="3"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="4"/>
+      <c r="A73" s="1"/>
       <c r="B73" s="3"/>
-      <c r="E73" s="4"/>
+      <c r="E73" s="1"/>
       <c r="F73" s="3"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
-      <c r="A74" s="4"/>
+      <c r="A74" s="1"/>
       <c r="B74" s="3"/>
-      <c r="E74" s="4"/>
+      <c r="E74" s="1"/>
       <c r="F74" s="3"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
-      <c r="A75" s="4"/>
+      <c r="A75" s="1"/>
       <c r="B75" s="3"/>
-      <c r="E75" s="4"/>
+      <c r="E75" s="1"/>
       <c r="F75" s="3"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="4"/>
+      <c r="A76" s="1"/>
       <c r="B76" s="3"/>
-      <c r="E76" s="4"/>
+      <c r="E76" s="1"/>
       <c r="F76" s="3"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
-      <c r="A77" s="4"/>
+      <c r="A77" s="1"/>
       <c r="B77" s="3"/>
-      <c r="E77" s="4"/>
+      <c r="E77" s="1"/>
       <c r="F77" s="3"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
-      <c r="A78" s="4"/>
+      <c r="A78" s="1"/>
       <c r="B78" s="3"/>
-      <c r="E78" s="4"/>
+      <c r="E78" s="1"/>
       <c r="F78" s="3"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c r="A79" s="4"/>
+      <c r="A79" s="1"/>
       <c r="B79" s="3"/>
-      <c r="E79" s="4"/>
+      <c r="E79" s="1"/>
       <c r="F79" s="3"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
-      <c r="A80" s="4"/>
+      <c r="A80" s="1"/>
       <c r="B80" s="3"/>
-      <c r="E80" s="4"/>
+      <c r="E80" s="1"/>
       <c r="F80" s="3"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="4"/>
+      <c r="A81" s="1"/>
       <c r="B81" s="3"/>
-      <c r="E81" s="4"/>
+      <c r="E81" s="1"/>
       <c r="F81" s="3"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="4"/>
+      <c r="A82" s="1"/>
       <c r="B82" s="3"/>
-      <c r="E82" s="4"/>
+      <c r="E82" s="1"/>
       <c r="F82" s="3"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
-      <c r="A83" s="4"/>
+      <c r="A83" s="1"/>
       <c r="B83" s="3"/>
-      <c r="E83" s="4"/>
+      <c r="E83" s="1"/>
       <c r="F83" s="3"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
-      <c r="A84" s="4"/>
+      <c r="A84" s="1"/>
       <c r="B84" s="3"/>
-      <c r="E84" s="4"/>
+      <c r="E84" s="1"/>
       <c r="F84" s="3"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
-      <c r="A85" s="4"/>
+      <c r="A85" s="1"/>
       <c r="B85" s="3"/>
-      <c r="E85" s="4"/>
+      <c r="E85" s="1"/>
       <c r="F85" s="3"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="4"/>
+      <c r="A86" s="1"/>
       <c r="B86" s="3"/>
-      <c r="E86" s="4"/>
+      <c r="E86" s="1"/>
       <c r="F86" s="3"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="4"/>
+      <c r="A87" s="1"/>
       <c r="B87" s="3"/>
-      <c r="E87" s="4"/>
+      <c r="E87" s="1"/>
       <c r="F87" s="3"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="4"/>
+      <c r="A88" s="1"/>
       <c r="B88" s="3"/>
-      <c r="E88" s="4"/>
+      <c r="E88" s="1"/>
       <c r="F88" s="3"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="4"/>
+      <c r="A89" s="1"/>
       <c r="B89" s="3"/>
-      <c r="E89" s="4"/>
+      <c r="E89" s="1"/>
       <c r="F89" s="3"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="4"/>
+      <c r="A90" s="1"/>
       <c r="B90" s="3"/>
-      <c r="E90" s="4"/>
+      <c r="E90" s="1"/>
       <c r="F90" s="3"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="4"/>
+      <c r="A91" s="1"/>
       <c r="B91" s="3"/>
-      <c r="E91" s="4"/>
+      <c r="E91" s="1"/>
       <c r="F91" s="3"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="4"/>
+      <c r="A92" s="1"/>
       <c r="B92" s="3"/>
-      <c r="E92" s="4"/>
+      <c r="E92" s="1"/>
       <c r="F92" s="3"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="4"/>
+      <c r="A93" s="1"/>
       <c r="B93" s="3"/>
-      <c r="E93" s="4"/>
+      <c r="E93" s="1"/>
       <c r="F93" s="3"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="4"/>
+      <c r="A94" s="1"/>
       <c r="B94" s="3"/>
-      <c r="E94" s="4"/>
+      <c r="E94" s="1"/>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="4"/>
+      <c r="A95" s="1"/>
       <c r="B95" s="3"/>
-      <c r="E95" s="4"/>
+      <c r="E95" s="1"/>
       <c r="F95" s="3"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="4"/>
+      <c r="A96" s="1"/>
       <c r="B96" s="3"/>
-      <c r="E96" s="4"/>
+      <c r="E96" s="1"/>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="4"/>
+      <c r="A97" s="1"/>
       <c r="B97" s="3"/>
-      <c r="E97" s="4"/>
+      <c r="E97" s="1"/>
       <c r="F97" s="3"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="4"/>
+      <c r="A98" s="1"/>
       <c r="B98" s="3"/>
-      <c r="E98" s="4"/>
+      <c r="E98" s="1"/>
       <c r="F98" s="3"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="4"/>
+      <c r="A99" s="1"/>
       <c r="B99" s="3"/>
-      <c r="E99" s="4"/>
+      <c r="E99" s="1"/>
       <c r="F99" s="3"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="4"/>
+      <c r="A100" s="1"/>
       <c r="B100" s="3"/>
-      <c r="E100" s="4"/>
+      <c r="E100" s="1"/>
       <c r="F100" s="3"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="4"/>
+      <c r="A101" s="1"/>
       <c r="B101" s="3"/>
-      <c r="E101" s="4"/>
+      <c r="E101" s="1"/>
       <c r="F101" s="3"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="4"/>
+      <c r="A102" s="1"/>
       <c r="B102" s="3"/>
-      <c r="E102" s="4"/>
+      <c r="E102" s="1"/>
       <c r="F102" s="3"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="4"/>
+      <c r="A103" s="1"/>
       <c r="B103" s="3"/>
-      <c r="E103" s="4"/>
+      <c r="E103" s="1"/>
       <c r="F103" s="3"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="4"/>
+      <c r="A104" s="1"/>
       <c r="B104" s="3"/>
-      <c r="E104" s="4"/>
+      <c r="E104" s="1"/>
       <c r="F104" s="3"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="4"/>
+      <c r="A105" s="1"/>
       <c r="B105" s="3"/>
-      <c r="E105" s="4"/>
+      <c r="E105" s="1"/>
       <c r="F105" s="3"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="4"/>
+      <c r="A106" s="1"/>
       <c r="B106" s="3"/>
-      <c r="E106" s="4"/>
+      <c r="E106" s="1"/>
       <c r="F106" s="3"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="4"/>
+      <c r="A107" s="1"/>
       <c r="B107" s="3"/>
-      <c r="E107" s="4"/>
+      <c r="E107" s="1"/>
       <c r="F107" s="3"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="4"/>
+      <c r="A108" s="1"/>
       <c r="B108" s="3"/>
-      <c r="E108" s="4"/>
+      <c r="E108" s="1"/>
       <c r="F108" s="3"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="4"/>
+      <c r="A109" s="1"/>
       <c r="B109" s="3"/>
-      <c r="E109" s="4"/>
+      <c r="E109" s="1"/>
       <c r="F109" s="3"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="4"/>
+      <c r="A110" s="1"/>
       <c r="B110" s="3"/>
-      <c r="E110" s="4"/>
+      <c r="E110" s="1"/>
       <c r="F110" s="3"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="4"/>
+      <c r="A111" s="1"/>
       <c r="B111" s="3"/>
-      <c r="E111" s="4"/>
+      <c r="E111" s="1"/>
       <c r="F111" s="3"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="4"/>
+      <c r="A112" s="1"/>
       <c r="B112" s="3"/>
-      <c r="E112" s="4"/>
+      <c r="E112" s="1"/>
       <c r="F112" s="3"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="4"/>
+      <c r="A113" s="1"/>
       <c r="B113" s="3"/>
-      <c r="E113" s="4"/>
+      <c r="E113" s="1"/>
       <c r="F113" s="3"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="4"/>
+      <c r="A114" s="1"/>
       <c r="B114" s="3"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="4"/>
+      <c r="A115" s="1"/>
       <c r="B115" s="3"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="4"/>
+      <c r="A116" s="1"/>
       <c r="B116" s="3"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="4"/>
+      <c r="A117" s="1"/>
       <c r="B117" s="3"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="4"/>
+      <c r="A118" s="1"/>
       <c r="B118" s="3"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="4"/>
+      <c r="A119" s="1"/>
       <c r="B119" s="3"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="4"/>
+      <c r="A120" s="1"/>
       <c r="B120" s="3"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="4"/>
+      <c r="A121" s="1"/>
       <c r="B121" s="3"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c r="A122" s="4"/>
+      <c r="A122" s="1"/>
       <c r="B122" s="3"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
-      <c r="A123" s="4"/>
+      <c r="A123" s="1"/>
       <c r="B123" s="3"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="4"/>
+      <c r="A124" s="1"/>
       <c r="B124" s="3"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
-      <c r="A125" s="4"/>
+      <c r="A125" s="1"/>
       <c r="B125" s="3"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="4"/>
+      <c r="A126" s="1"/>
       <c r="B126" s="3"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="4"/>
+      <c r="A127" s="1"/>
       <c r="B127" s="3"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
-      <c r="A128" s="4"/>
+      <c r="A128" s="1"/>
       <c r="B128" s="3"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="4"/>
+      <c r="A129" s="1"/>
       <c r="B129" s="3"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="4"/>
+      <c r="A130" s="1"/>
       <c r="B130" s="3"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="4"/>
+      <c r="A131" s="1"/>
       <c r="B131" s="3"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="4"/>
+      <c r="A132" s="1"/>
       <c r="B132" s="3"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="4"/>
+      <c r="A133" s="1"/>
       <c r="B133" s="3"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="4"/>
+      <c r="A134" s="1"/>
       <c r="B134" s="3"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="4"/>
+      <c r="A135" s="1"/>
       <c r="B135" s="3"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="4"/>
+      <c r="A136" s="1"/>
       <c r="B136" s="3"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
-      <c r="A137" s="4"/>
+      <c r="A137" s="1"/>
       <c r="B137" s="3"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="4"/>
+      <c r="A138" s="1"/>
       <c r="B138" s="3"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="4"/>
+      <c r="A139" s="1"/>
       <c r="B139" s="3"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="4"/>
+      <c r="A140" s="1"/>
       <c r="B140" s="3"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="4"/>
+      <c r="A141" s="1"/>
       <c r="B141" s="3"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="4"/>
+      <c r="A142" s="1"/>
       <c r="B142" s="3"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="4"/>
+      <c r="A143" s="1"/>
       <c r="B143" s="3"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="4"/>
+      <c r="A144" s="1"/>
       <c r="B144" s="3"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="4"/>
+      <c r="A145" s="1"/>
       <c r="B145" s="3"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="4"/>
+      <c r="A146" s="1"/>
       <c r="B146" s="3"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="4"/>
+      <c r="A147" s="1"/>
       <c r="B147" s="3"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c r="A148" s="4"/>
+      <c r="A148" s="1"/>
       <c r="B148" s="3"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="4"/>
+      <c r="A149" s="1"/>
       <c r="B149" s="3"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="4"/>
+      <c r="A150" s="1"/>
       <c r="B150" s="3"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="4"/>
+      <c r="A151" s="1"/>
       <c r="B151" s="3"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="4"/>
+      <c r="A152" s="1"/>
       <c r="B152" s="3"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="4"/>
+      <c r="A153" s="1"/>
       <c r="B153" s="3"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="4"/>
+      <c r="A154" s="1"/>
       <c r="B154" s="3"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="4"/>
+      <c r="A155" s="1"/>
       <c r="B155" s="3"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="4"/>
+      <c r="A156" s="1"/>
       <c r="B156" s="3"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="4"/>
+      <c r="A157" s="1"/>
       <c r="B157" s="3"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="4"/>
+      <c r="A158" s="1"/>
       <c r="B158" s="3"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="4"/>
+      <c r="A159" s="1"/>
       <c r="B159" s="3"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="4"/>
+      <c r="A160" s="1"/>
       <c r="B160" s="3"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="4"/>
+      <c r="A161" s="1"/>
       <c r="B161" s="3"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="4"/>
+      <c r="A162" s="1"/>
       <c r="B162" s="3"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="4"/>
+      <c r="A163" s="1"/>
       <c r="B163" s="3"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="4"/>
+      <c r="A164" s="1"/>
       <c r="B164" s="3"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="4"/>
+      <c r="A165" s="1"/>
       <c r="B165" s="3"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
-      <c r="A166" s="4"/>
+      <c r="A166" s="1"/>
       <c r="B166" s="3"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="4"/>
+      <c r="A167" s="1"/>
       <c r="B167" s="3"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="4"/>
+      <c r="A168" s="1"/>
       <c r="B168" s="3"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="4"/>
+      <c r="A169" s="1"/>
       <c r="B169" s="3"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="4"/>
+      <c r="A170" s="1"/>
       <c r="B170" s="3"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="4"/>
+      <c r="A171" s="1"/>
       <c r="B171" s="3"/>
     </row>
     <row r="172" ht="14.25" customHeight="1"/>
@@ -9322,64 +9262,59 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.29"/>
-    <col customWidth="1" min="2" max="2" width="14.14"/>
-    <col customWidth="1" min="3" max="3" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="14.14" customWidth="1"/>
+    <col min="3" max="3" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15.0" customHeight="1">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="15.0" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -9387,41 +9322,36 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A3"/>
+    <hyperlink ref="A3" r:id="rId1"/>
   </hyperlinks>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="29.43"/>
-    <col customWidth="1" min="2" max="2" width="31.43"/>
-    <col customWidth="1" min="3" max="3" width="28.71"/>
-    <col customWidth="1" min="4" max="4" width="30.57"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
+    <col min="1" max="1" width="29.43" customWidth="1"/>
+    <col min="2" max="2" width="31.43" customWidth="1"/>
+    <col min="3" max="3" width="28.71" customWidth="1"/>
+    <col min="4" max="4" width="30.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -9429,16 +9359,16 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -9446,16 +9376,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -9463,16 +9393,16 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -9480,16 +9410,16 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -9497,404 +9427,391 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.29"/>
-    <col customWidth="1" min="2" max="2" width="20.14"/>
-    <col customWidth="1" min="3" max="4" width="13.57"/>
-    <col customWidth="1" min="5" max="5" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="20.14" customWidth="1"/>
+    <col min="3" max="4" width="13.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.57"/>
-    <col customWidth="1" min="2" max="2" width="39.86"/>
-    <col customWidth="1" min="3" max="3" width="14.43"/>
+    <col min="1" max="1" width="27.57" customWidth="1"/>
+    <col min="2" max="2" width="39.86" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="56.0"/>
-    <col customWidth="1" min="2" max="2" width="57.0"/>
-    <col customWidth="1" min="3" max="3" width="14.43"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/UAA/src/src/test/resources/com/ugapp/data/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/data/testdata.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\divya\git\undergrad\UAA\src\src\test\resources\com\ugapp\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\divya\git\undergrad\UAA\src\src\test\resources\com\ugapp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="test_suite" sheetId="1" r:id="rId1"/>
@@ -67,26 +67,6 @@
   </si>
   <si>
     <t>overAllAcademicsTest</t>
-  </si>
-  <si>
-    <t>Legal sex</t>
-  </si>
-  <si>
-    <t>X or another legal sex</t>
-  </si>
-  <si>
-    <t>Primary language spoken at home</t>
-  </si>
-  <si>
-    <t>Bavarian</t>
-  </si>
-  <si>
-    <t>Home address</t>
-  </si>
-  <si>
-    <t>Test Address line1 Test Address line2
-TestTestTestTestTestTestTestTest,Test State,Mayotte
-12345-678910</t>
   </si>
   <si>
     <t>email</t>
@@ -2397,25 +2377,25 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2423,25 +2403,25 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>3</v>
@@ -2449,25 +2429,25 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>72</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>3</v>
@@ -2495,19 +2475,19 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -2515,19 +2495,19 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -2535,19 +2515,19 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
@@ -2575,16 +2555,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -2592,16 +2572,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -2609,16 +2589,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -2642,16 +2622,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -2659,16 +2639,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -2676,16 +2656,16 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -2693,16 +2673,16 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -2710,16 +2690,16 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -2727,16 +2707,16 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
@@ -2744,16 +2724,16 @@
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>3</v>
@@ -2761,16 +2741,16 @@
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
@@ -2778,16 +2758,16 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>3</v>
@@ -2795,16 +2775,16 @@
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -2828,13 +2808,13 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -2842,13 +2822,13 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
@@ -2856,13 +2836,13 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -2870,13 +2850,13 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -2885,10 +2865,10 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -2897,10 +2877,10 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="11"/>
       <c r="B6" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -2928,16 +2908,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -2945,16 +2925,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -2962,16 +2942,16 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -3067,12 +3047,7 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="B8" s="4"/>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
       <c r="F8" s="3"/>
@@ -3081,12 +3056,7 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="B9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
       <c r="F9" s="3"/>
@@ -3095,12 +3065,7 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="137.25" customHeight="1">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="B10" s="4"/>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
       <c r="F10" s="3"/>
@@ -9278,10 +9243,10 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -9289,10 +9254,10 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -9300,10 +9265,10 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -9311,10 +9276,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -9342,16 +9307,16 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -9359,16 +9324,16 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -9376,16 +9341,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -9393,16 +9358,16 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -9410,16 +9375,16 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -9427,16 +9392,16 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
@@ -9460,16 +9425,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -9477,16 +9442,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -9494,16 +9459,16 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -9511,16 +9476,16 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -9528,16 +9493,16 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -9563,10 +9528,10 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -9574,10 +9539,10 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -9585,10 +9550,10 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -9596,10 +9561,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -9607,10 +9572,10 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -9618,10 +9583,10 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -9629,10 +9594,10 @@
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -9640,10 +9605,10 @@
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -9651,10 +9616,10 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -9662,10 +9627,10 @@
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -9673,10 +9638,10 @@
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -9684,10 +9649,10 @@
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -9695,10 +9660,10 @@
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -9706,10 +9671,10 @@
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -9717,10 +9682,10 @@
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -9746,10 +9711,10 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -9757,10 +9722,10 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -9768,10 +9733,10 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -9779,10 +9744,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -9790,10 +9755,10 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -9801,10 +9766,10 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
